--- a/output_AO/Raport_Oferta_3.xlsx
+++ b/output_AO/Raport_Oferta_3.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>373</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D415"/>
+  <dimension ref="A1:D391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Categoria de lucrari: INSTALATII SANITARE OB.2</t>
+          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA CUPOLA TEREN TENIS</t>
         </is>
       </c>
     </row>
@@ -612,122 +612,122 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
+          <t>TSC18B1  mc  2.5
+SAPAT. CU BULDOZ. PE TRACT. 65-80CP INCL. IMPINS PAMINTULUI LA 10 M TEREN CAT 2</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>TSC18B1  mc  0.7
+SAPAT.CU BULDOZ. PE TRACT. 65-80CP INCL. IMPINS PAMINTULUI LA 10 M TEREN CAT 2 material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>CANTITATE DIFERITĂ
+Ref: 2.5  |  Ofertă: 0.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>$2100910  mc  18.144
+BETON MARFA CLASA C8/10</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>$2100910  mc  15.12
+BETON MARFA CLASA C8 / 10 Deviz "001" - Formular F3 Formular generat cu programuf @Devize (www.eDevize.ro)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>CANTITATE DIFERITĂ
+Ref: 18.144  |  Ofertă: 15.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CA01J1  mc  18.0
+TURNARE BETON SIMPLU IN STRATURI DE 5- 20CM PT.EGALIZARI LA CONSTRUCTII EDILITARE (APEDUCTE, CANALE</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>CA02A1  mc  55.0
+TURNARE BETON ARMAT IN FUNDATII IZOLATE CU VOLUM &lt;3MC</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII SANITARE OB.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>AUT3000  ora  2.0
 APARAT DE SUDURA TIP , , COPRAX' ' 2204/ 50Hz/700w</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>AUT3000  ora  3.2
 APARAT DE SUDURA TIP,, COPRAX ' ' 2204 / 50Hz / 700w material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>CANTITATE DIFERITĂ
 Ref: 2.0  |  Ofertă: 3.2</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: INSTALATII ELECTRICE tari OB.2 curenti</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>$3270431  m  3.0
-CABLU CYYF 3X2,5 DESIGN STUDIO S.R.L. 650_ 09obiect inițial 424/2018 - proiect actualizat integral 424-rev / 2024 EC05A1 M CABLU ENERGIE TRAS PRIN TUB PROT METAL PT RACORD MOTOARE TABLOURI APARATE CONDUCTE &lt; 16 MMP. *</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>$3270431  m  650.0
-CABLU CYYF 3X2,5</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>CANTITATE DIFERITĂ
-Ref: 3.0  |  Ofertă: 650.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII SANITARE OB. 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>AUT3000  ora  2.0
-APARAT DE SUDURA TIP , , COPRAX' ' 2204/ 50Hz/700w</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>AUT3000  ora  2.8
-APARAT DE SUDURA TIP COPRAX2204 / 50Hz / 700w material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>CANTITATE DIFERITĂ
-Ref: 2.0  |  Ofertă: 2.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>$3270242  buc  10.0
-REDUCTIE PPR 32-25</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>$3270394  buc  25.0
-COT 90 GRD. INTERIOR - EXTERIOR PPR 25</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -737,18 +737,20 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3270431  m  3.0
+CABLU CYYF 3X2,5 DESIGN STUDIO S.R.L. 650_ 09obiect inițial 424/2018 - proiect actualizat integral 424-rev / 2024 EC05A1 M CABLU ENERGIE TRAS PRIN TUB PROT METAL PT RACORD MOTOARE TABLOURI APARATE CONDUCTE &lt; 16 MMP. *</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$3271730  m  10.0
-TEAVA PN20 PPR VERDE DN25</t>
+          <t>$3270431  m  650.0
+CABLU CYYF 3X2,5</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>CANTITATE DIFERITĂ
+Ref: 3.0  |  Ofertă: 650.0</t>
         </is>
       </c>
     </row>
@@ -758,18 +760,20 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EC05B1  m  550.0
+CABLU ENERGIE TRAS PRIN TUB PROT METAL PT RACORD MOTOARE TABLOURI APARATE CONDUCTE 25 SAU 35 MMP</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>$3270242  buc  1.0
-REDUCTIE PPR 32-25</t>
+          <t>EC05B1  m  1450.0
+CABLU ENERGIE TRAS PRIN TUB PROT METAL PT RACORD MOTOARE TABLOURI APARATE CONDUCTE 25 SAU 35 MMP material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>CANTITATE DIFERITĂ
+Ref: 550.0  |  Ofertă: 1450.0</t>
         </is>
       </c>
     </row>
@@ -779,130 +783,134 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3270430  m  550.0
+CABLU CYYF 3X1 5</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$3271730  m  76.5
-TEAVA PN20 PPR VERDE DN25</t>
+          <t>$3270430  m  95.0
+CABLU CYYF 3X1 5</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>$3270394  buc  20.0
-COT 90 GRD. INTERIOR - EXTERIOR PPR 25</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>CANTITATE DIFERITĂ
+Ref: 550.0  |  Ofertă: 95.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII SANITARE OB. 4</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>AUT3000  ora  2.0
+APARAT DE SUDURA TIP , , COPRAX' ' 2204/ 50Hz/700w</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>AUT3000  ora  2.8
+APARAT DE SUDURA TIP COPRAX2204 / 50Hz / 700w material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul Devize (www.eDevize.ro)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>CANTITATE DIFERITĂ
+Ref: 2.0  |  Ofertă: 2.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>$3270242  buc  10.0
+REDUCTIE PPR 32-25</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>$3270242  buc  15.0
 REDUCTIE PPR 32-25</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>$3270394  buc  5.0
 COT 90 GRD. INTERIOR - EXTERIOR PPR 25</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>$3271730  m  40.8
 TEAVA PN20 PPR VERDE DN25</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>SA14B#  ml  70.0
-TEAVA MAT PL (PP, PE, PP - R) IMBINARE PRIN SUDURA PRIN POLIFUZIUNE, LA CTII IND, D = 20 MM material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: 45000000 UTILITATI-RETELE EXTERIOARE</t>
         </is>
       </c>
     </row>
@@ -912,20 +920,18 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>TRA01A20  tona  122.4
-TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOBASCULANTA PE DIST .= 20 KM.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TRA01A20  km  122.4
-TRANSPORTUL RUTIER AL MATERIALELOR, SEMI FABRICATELOR CU AUTOBASCULANTA PE DIST. 20 TONA material: manopera: utilaj: transport:</t>
+          <t>$3271730  m  76.5
+TEAVA PN20 PPR VERDE DN25</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>UNITATE DE MĂSURĂ DIFERITĂ
-Ref: tona  |  Ofertă: km</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -935,18 +941,18 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>TCC23B1  buc  15.0
-INSTALATIE DE TV IN CIRCUIT INCHIS : MONITOR VIDEOCAMONTARE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3270242  buc  1.0
+REDUCTIE PPR 32-25</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -956,18 +962,18 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  1.0
-APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3271730  m  10.0
+TEAVA PN20 PPR VERDE DN25</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -982,8 +988,8 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>W2H04A1  mc  68.0
-STRAT NISIP ASEZAT IN SANT PENTRU PROTEJAREA CABLURILOR LA LUCR IN PROF NETIPIZAT material: manopera: utilaj: transport:</t>
+          <t>$3270394  buc  20.0
+COT 90 GRD. INTERIOR - EXTERIOR PPR 25</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -1003,8 +1009,8 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>$3272541  m  100.0
-TUB PROTECTIE CABLU D.110 GOFRAT ALBASTRU DUBLU STRAT 450N L6M Deviz "003" - Formular F3</t>
+          <t>$3270394  buc  25.0
+COT 90 GRD. INTERIOR - EXTERIOR PPR 25</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1013,52 +1019,56 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>W2G02B31  m  100.0
-MONT. CABLU SUBT.1 KV GR 2,901-3,200 KG / M CU - AL IN TUB PE TRASEU CU OBST. TR. MANUALA MONT material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: 45000000 EXTINDERE SI MODERNIZARE BAZA SPORTIVA RACARI UTILITATI-RETELE EXTERIOARE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ACD04A1  buc  8.0
+CAMIN VIZITARE STAS 2448-73 CU CAMERA LUCRU HC=2M DIN TUB BET. CU CEP SI BUZA LA CANALE CU DN 200</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>ACD04A1  buc  1.0
+CAMIN VIZITARE STAS 2448-73 CU CAMERA LUCRU HC = 2M DIN TUB BET. CU CEP SI BUZA LA CANALE CU DN 200 material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>CANTITATE DIFERITĂ
+Ref: 8.0  |  Ofertă: 1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>$3274594  buc  1.0
-CAMIN DUBLUSTRAT PT. APOMETRU CU INSTALATIE 3/4 ' ' SI CAPAC D.550 H.1100MM Deviz "001" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro) Pagina 1 din 4</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: 45000000 EXTINDERE SI MODERNIZARE BAZA SPORTIVA RACARI UTILITATI-RETELE EXTERIOARE</t>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>TSC02A11  mc  1.4
+MC PAMINT UMID.NATUR.DESC.DEP. TER. CAT. 1 IN COND. GOSP.APE DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>TSC02A11  mc  0.5
+SAPATURA CU EXCAVAT. PE PNEURI 0,21-0,39 MC PAMINT UMID.NATUR.DESC.DEP.TER.CAT. 1 IN COND.GOSP.APE material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>CANTITATE DIFERITĂ
+Ref: 1.4  |  Ofertă: 0.5</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1078,18 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ACD04A1  buc  8.0
-CAMIN VIZITARE STAS 2448-73 CU CAMERA LUCRU HC=2M DIN TUB BET. CU CEP SI BUZA LA CANALE CU DN 200</t>
+          <t>ACA10D1  m  190.0
+MONTARE TEAVA PVC TIP 4 (G) IN PAMINT IN EXTERIORULCLADIRILOR, AVIND DN 110</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>ACD04A1  buc  1.0
-CAMIN VIZITARE STAS 2448-73 CU CAMERA LUCRU HC = 2M DIN TUB BET. CU CEP SI BUZA LA CANALE CU DN 200 material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>CANTITATE DIFERITĂ
-Ref: 8.0  |  Ofertă: 1.0</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -1091,20 +1099,18 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>TSC02A11  mc  1.4
-MC PAMINT UMID.NATUR.DESC.DEP. TER. CAT. 1 IN COND. GOSP.APE DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>$3270476  m  188.5
+TEAVA PVC-KG 110X3. 0x1000</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>TSC02A11  mc  0.5
-SAPATURA CU EXCAVAT. PE PNEURI 0,21-0,39 MC PAMINT UMID.NATUR.DESC.DEP.TER.CAT. 1 IN COND.GOSP.APE material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>CANTITATE DIFERITĂ
-Ref: 1.4  |  Ofertă: 0.5</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -1114,8 +1120,8 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ACA10D1  m  190.0
-MONTARE TEAVA PVC TIP 4 (G) IN PAMINT IN EXTERIORULCLADIRILOR, AVIND DN 110</t>
+          <t>$3270000  buc  8.0
+CAMIN PVC BASIC LINE D=1000 mm, alcatuit din bazin colectare, inel intermedial, piesa superioara, inel beton</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -1135,8 +1141,8 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>$3270476  m  188.5
-TEAVA PVC-KG 110X3. 0x1000</t>
+          <t>ACD01L1  buc  8.0
+CAPAC SI RAMA STAS 2308-81 PENTRU CAMINE CU PIESA SUPORT CAROSABIL IV</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1156,8 +1162,8 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>$3270000  buc  8.0
-CAMIN PVC BASIC LINE D=1000 mm, alcatuit din bazin colectare, inel intermedial, piesa superioara, inel beton</t>
+          <t>DF26A1  m  198.0
+Banda de semnalizare</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -1177,8 +1183,8 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ACD01L1  buc  8.0
-CAPAC SI RAMA STAS 2308-81 PENTRU CAMINE CU PIESA SUPORT CAROSABIL IV</t>
+          <t>$3270513  m  198.0
+BANDA AVERTIZARE &lt;KOMPACTKIT&gt; CANAL 11, 5CMX 0,17MM</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1192,72 +1198,102 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>DF26A1  m  198.0
-Banda de semnalizare</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: 45000000 UTILITATI-RETELE EXTERIOARE</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>TRA01A20  tona  122.4
+TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOBASCULANTA PE DIST .= 20 KM.</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>TRA01A20  km  122.4
+TRANSPORTUL RUTIER AL MATERIALELOR, SEMI FABRICATELOR CU AUTOBASCULANTA PE DIST. 20 TONA material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>UNITATE DE MĂSURĂ DIFERITĂ
+Ref: tona  |  Ofertă: km</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>$3270513  m  198.0
-BANDA AVERTIZARE &lt;KOMPACTKIT&gt; CANAL 11, 5CMX 0,17MM</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>TCC23B1  buc  15.0
+INSTALATIE DE TV IN CIRCUIT INCHIS : MONITOR VIDEOCAMONTARE</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>TCB40A1  buc  1.0
+APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: ARHITECTURA GRADENE</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>IZDO3D1  tona  8.0
 VOPSIRE CU VOPS MINIU CU APARAT AER COMPR 1 STR PECONF SI CTII METAL EXEC DIN PROF GROS 8-12 MM DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>IZD03D1  tona  8.0
 VOPSIRE CU VOPS MINIU CU APARAT AER COMPR 1 STR PECONF SI CTII METAL EXEC DIN PROF GROS 8-12 MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>COD SIMILAR — posibilă eroare OCR sau variație
 Ref: IZDO3D1  |  Ofertat: IZD03D1
@@ -1265,80 +1301,52 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>IZD04D1  tona  8.0
-VOPSIRE CU APARAT AER COMPR VOPSEA ULEI PE CONF SICONSTR MET PROFILE 8-12MM 2STRATURI material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA CUPOLA TEREN TENIS</t>
-        </is>
-      </c>
-    </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="7" t="n">
         <v>31</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>CA01J1  mc  18.0
-TURNARE BETON SIMPLU IN STRATURI DE 5- 20CM PT.EGALIZARI LA CONSTRUCTII EDILITARE (APEDUCTE, CANALE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>IZD04D1  tona  8.0
+VOPSIRE CU APARAT AER COMPR VOPSEA ULEI PE CONF SICONSTR MET PROFILE 8-12MM 2STRATURI material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="7" t="n">
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: ARHITECTURA -teren tenis acoperi t</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>CA02A1  mc  55.0
-TURNARE BETON ARMAT IN FUNDATII IZOLATE CU VOLUM &lt;3MC</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: ARHITECTURA -teren tenis acoperi t</t>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>RPCE29A#  mp  1256.0
+PRELATA PENTRU PROTEJAREA TERASEI PE TIMP PLOIOS PE DURATA REFACERII</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -1348,8 +1356,8 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>RPCE29A#  mp  1256.0
-PRELATA PENTRU PROTEJAREA TERASEI PE TIMP PLOIOS PE DURATA REFACERII</t>
+          <t>$3999988  mp  0.0
+DESIGN STUDIO S.R.L. - proiect inițial 424/2018 PRELATA SPECIALA ANTIVANT, REZISTENT LA FOC, LA UMIDITATE SI MUCEGAI 424-rev/ 2024 12/56. 000 proiect actualizat integral</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -1369,8 +1377,8 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>$3999988  mp  0.0
-DESIGN STUDIO S.R.L. - proiect inițial 424/2018 PRELATA SPECIALA ANTIVANT, REZISTENT LA FOC, LA UMIDITATE SI MUCEGAI 424-rev/ 2024 12/56. 000 proiect actualizat integral</t>
+          <t>CK25A#  mp  7.0
+USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -1390,8 +1398,8 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>CK25A#  mp  7.0
-USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
+          <t>$6306431  mp  7.0
+USI DIN PVC</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1411,8 +1419,8 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>$6306431  mp  7.0
-USI DIN PVC</t>
+          <t>CE23A1  mp  1256.0
+PLASA DE SIGURANTA REFOLOS. LA EXEC. INVELITORI CONSSTRUCTII</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -1432,8 +1440,8 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>CE23A1  mp  1256.0
-PLASA DE SIGURANTA REFOLOS. LA EXEC. INVELITORI CONSSTRUCTII</t>
+          <t>$2941123  mp  1256.0
+PLASA TEXTILA 2 MM PENTRU CUPOLE TEREN</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1453,46 +1461,46 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>$2941123  mp  1256.0
-PLASA TEXTILA 2 MM PENTRU CUPOLE TEREN</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
           <t>TRB05B23  tona  25.0
 TRANSPORTUL MATERIALELOR PRIN PURTAT DIRECT, MATERIALE INCOMODE PESTE 25 KG DISTANTA 30M</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Categoria de lucrari: </t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>IZF17A1  mp  230.0
+TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -1502,8 +1510,8 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>IZF17A1  mp  230.0
-TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
+          <t>$3271283  mp  234.6
+VATA MINERALA BAZALTICA 40 KG/M3 , 10 CM 1 BAX=2, 4M2</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -1523,8 +1531,8 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>$3271283  mp  234.6
-VATA MINERALA BAZALTICA 40 KG/M3 , 10 CM 1 BAX=2, 4M2</t>
+          <t>CK26C1  buc  1380.0
+DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -1544,8 +1552,8 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>CK26C1  buc  1380.0
-DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
+          <t>$3274531  buc  1840.0
+DIBLURI DE POLISTIREN 150 MM</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -1565,8 +1573,8 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>$3274531  buc  1840.0
-DIBLURI DE POLISTIREN 150 MM</t>
+          <t>RPCE26C1  mp  230.0
+PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -1586,8 +1594,8 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>RPCE26C1  mp  230.0
-PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
+          <t>$3274536  mp  253.0
+PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -1607,8 +1615,8 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>$3274536  mp  253.0
-PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
+          <t>CF06B1  mp  230.0
+TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE ZIDURI, IN GROSIME MEDIE DE 2,5CM</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -1628,8 +1636,8 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>CF06B1  mp  230.0
-TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE ZIDURI, IN GROSIME MEDIE DE 2,5CM</t>
+          <t>$2101131  kg  1840.0
+@MORTAR ADEZIV PT PLACI TERMOIZOLANTE</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -1649,8 +1657,8 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>$2101131  kg  1840.0
-@MORTAR ADEZIV PT PLACI TERMOIZOLANTE</t>
+          <t>$3274532  kg  34.5
+VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -1670,8 +1678,8 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>$3274532  kg  34.5
-VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
+          <t>CN06A1  mp  230.0
+VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -1691,8 +1699,8 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>CN06A1  mp  230.0
-VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
+          <t>$6104676  kg  736.0
+VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -1712,8 +1720,8 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>$6104676  kg  736.0
-VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
+          <t>CF24A1  mp  79.0
+PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -1733,8 +1741,8 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>CF24A1  mp  79.0
-PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
+          <t>$2100843  mp  0.0
+@PLACA RB 12,5 MM -82.160</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -1754,8 +1762,8 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>$2100843  mp  0.0
-@PLACA RB 12,5 MM -82.160</t>
+          <t>$2100853  mp  82.16
+@PLACA RBI 12,5 MM</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -1775,8 +1783,8 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>$2100853  mp  82.16
-@PLACA RBI 12,5 MM</t>
+          <t>CF10C1  mp  79.0
+GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -1796,8 +1804,8 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>CF10C1  mp  79.0
-GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
+          <t>$3273908  buc  3.0
+CACIULA VENTILATIE KADH 75MM</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -1817,8 +1825,8 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>$3273908  buc  3.0
-CACIULA VENTILATIE KADH 75MM</t>
+          <t>RPSB58E1  buc  3.0
+INLOC. CACIULA DE VENT.DE TB PE COLOAN.DE AERISIREDIN TUB FONT. PVC SAU GRESIE CERAM. AVIND D= 150M</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -1838,8 +1846,8 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>RPSB58E1  buc  3.0
-INLOC. CACIULA DE VENT.DE TB PE COLOAN.DE AERISIREDIN TUB FONT. PVC SAU GRESIE CERAM. AVIND D= 150M</t>
+          <t>$3276843  buc  3.0
+AERATOR POLIPROPILENA CU MEMBRANA TIA D.</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -1859,8 +1867,8 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>$3276843  buc  3.0
-AERATOR POLIPROPILENA CU MEMBRANA TIA D.</t>
+          <t>SF02C#  m  70.0
+EFECTUARE PROBA FUNCT INSTAL APA RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D=16-110 MM SF05C# M SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -1880,8 +1888,8 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>SF02C#  m  70.0
-EFECTUARE PROBA FUNCT INSTAL APA RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D=16-110 MM SF05C# M SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
+          <t>ACA17A1  buc  2.0
+PIESA LEGATURA DIN POLIESTERI ARMATE CU FIBRE STICLA AVIND GREUTATEA PE BUCATA PINA LA INC. 10 K</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -1901,8 +1909,8 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ACA17A1  buc  2.0
-PIESA LEGATURA DIN POLIESTERI ARMATE CU FIBRE STICLA AVIND GREUTATEA PE BUCATA PINA LA INC. 10 K</t>
+          <t>$3274797  buc  2.0
+REDUCTIE EXCENTRICA 110/50 /TEVI SI FITINGURI PP IGNIFUGATE CU GARNITURA PENTRU RETELE DE SCURGERI INTERIOARE SI TEVI DIN PVC</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -1922,8 +1930,8 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>$3274797  buc  2.0
-REDUCTIE EXCENTRICA 110/50 /TEVI SI FITINGURI PP IGNIFUGATE CU GARNITURA PENTRU RETELE DE SCURGERI INTERIOARE SI TEVI DIN PVC</t>
+          <t>SF04A#  m  105.0
+EF PRB ETANS , FUNCT, INST CANAL DIN TUB FONTA SC, TEVI PVC (U) , PE, PP, PP-R FONTA DUCT.D=100MM BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -1943,8 +1951,8 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>SF04A#  m  105.0
-EF PRB ETANS , FUNCT, INST CANAL DIN TUB FONTA SC, TEVI PVC (U) , PE, PP, PP-R FONTA DUCT.D=100MM BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
+          <t>SC07A1  buc  9.0
+LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -1964,8 +1972,8 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>SC07A1  buc  9.0
-LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
+          <t>$2438407  buc  9.0
+LAVOAR PORTELAN</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -1985,8 +1993,8 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>$2438407  buc  9.0
-LAVOAR PORTELAN</t>
+          <t>SC19B1  buc  9.0
+SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -2006,8 +2014,8 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>SC19B1  buc  9.0
-SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
+          <t>$4202797  buc  9.0
+SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -2027,8 +2035,8 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>$4202797  buc  9.0
-SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
+          <t>SC25A1  buc  9.0
+ETAJERA DIN PORTELAN SANITAR TIP</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -2048,8 +2056,8 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>SC25A1  buc  9.0
-ETAJERA DIN PORTELAN SANITAR TIP</t>
+          <t>$2451875  buc  9.0
+ETAJERA PORTELAN TIP E2.60 ALB C.2 NI</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -2069,8 +2077,8 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>$2451875  buc  9.0
-ETAJERA PORTELAN TIP E2.60 ALB C.2 NI</t>
+          <t>SC26A1  buc  9.0
+OGLINDA SANIT. SEMICRIST.MARGINI . SLEF.CU DIMENS . 400×500MM</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -2090,8 +2098,8 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>SC26A1  buc  9.0
-OGLINDA SANIT. SEMICRIST.MARGINI . SLEF.CU DIMENS . 400×500MM</t>
+          <t>$2222224  buc  9.0
+OGLINDA</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
@@ -2111,8 +2119,8 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>$2222224  buc  9.0
-OGLINDA</t>
+          <t>SC31A1  buc  9.0
+VENTIL DE SCURGERE TIP</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -2132,8 +2140,8 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>SC31A1  buc  9.0
-VENTIL DE SCURGERE TIP</t>
+          <t>$4203179  buc  9.0
+VENTIL SCURGERE LAVOAR, BIDEU 1 1/4 FARA RACORD S 411</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
@@ -2153,8 +2161,8 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>$4203179  buc  9.0
-VENTIL SCURGERE LAVOAR, BIDEU 1 1/4 FARA RACORD S 411</t>
+          <t>SD06A1  buc  9.0
+BATERIE AMESTECATOARE, STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -2174,8 +2182,8 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>SD06A1  buc  9.0
-BATERIE AMESTECATOARE, STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
+          <t>$3272003  buc  9.0
+BATERIE MONOCOMANDA PENTRU LAVOAR</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
@@ -2195,8 +2203,8 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>$3272003  buc  9.0
-BATERIE MONOCOMANDA PENTRU LAVOAR</t>
+          <t>SD12A1  buc  18.0
+ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -2216,8 +2224,8 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>SD12A1  buc  18.0
-ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
+          <t>$4201779  buc  18.0
+ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
         </is>
       </c>
       <c r="C89" s="8" t="inlineStr">
@@ -2237,8 +2245,8 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>$4201779  buc  18.0
-ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
+          <t>SC28B1  buc  9.0
+SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -2258,8 +2266,8 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>SC28B1  buc  9.0
-SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
+          <t>$2222225  buc  9.0
+DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
@@ -2279,8 +2287,8 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>$2222225  buc  9.0
-DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
+          <t>SC24A1  buc  9.0
+PORTPROSOP DIN AM NICHEL. MONT . PE PERETI TIP U,CU 1 BRAT, DESCHID. 450MM</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -2300,8 +2308,8 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>SC24A1  buc  9.0
-PORTPROSOP DIN AM NICHEL. MONT . PE PERETI TIP U,CU 1 BRAT, DESCHID. 450MM</t>
+          <t>$2222227  buc  9.0
+DISPENSER INOX SERVETELE HARTIE BUC. MONTAT LAVOAR PERSOANE CU DIZABIL</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
@@ -2321,8 +2329,8 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>$2222227  buc  9.0
-DISPENSER INOX SERVETELE HARTIE BUC. MONTAT LAVOAR PERSOANE CU DIZABIL</t>
+          <t>SC04A#  buc  1.0
+LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -2342,8 +2350,8 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>SC04A#  buc  1.0
-LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
+          <t>$2222215  buc  1.0
+LAVOAR PERSOANE CU DISABILITATI</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -2363,8 +2371,8 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>$2222215  buc  1.0
-LAVOAR PERSOANE CU DISABILITATI</t>
+          <t>TCC18C1  buc  1.0
+DISPOZITIV DE MONTARE A GHIDULUI DE UNDA: CONSOLA MONTARE</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -2384,8 +2392,8 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>TCC18C1  buc  1.0
-DISPOZITIV DE MONTARE A GHIDULUI DE UNDA: CONSOLA MONTARE</t>
+          <t>$2222217  buc  1.0
+BARA SPRIJINI PERSOANE CU DIZABILITATI</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
@@ -2405,8 +2413,8 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>$2222217  buc  1.0
-BARA SPRIJINI PERSOANE CU DIZABILITATI</t>
+          <t>SD04A#  buc  1.0
+BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -2426,8 +2434,8 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>SD04A#  buc  1.0
-BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
+          <t>$2222216  buc  1.0
+BATERIE LAVOAR PERSOANE CU DISABILITATI</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
@@ -2447,8 +2455,8 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>$2222216  buc  1.0
-BATERIE LAVOAR PERSOANE CU DISABILITATI</t>
+          <t>$4203301  buc  1.0
+VENTIL SCURGERE LAVOAR, SPALATOR 1"" FARA RACORD S9610</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -2468,8 +2476,8 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>$4203301  buc  1.0
-VENTIL SCURGERE LAVOAR, SPALATOR 1"" FARA RACORD S9610</t>
+          <t>$4202761  buc  1.0
+SIFON ALAMA PENTRU LAVOAR 1"" S 9611</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
@@ -2489,8 +2497,8 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>$4202761  buc  1.0
-SIFON ALAMA PENTRU LAVOAR 1"" S 9611</t>
+          <t>SD05A1  buc  2.0
+ROBINET PENTRU LAVOAR TIP AVIND DIAMETRUL DE 1/2 TOLI</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
@@ -2510,8 +2518,8 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>SD05A1  buc  2.0
-ROBINET PENTRU LAVOAR TIP AVIND DIAMETRUL DE 1/2 TOLI</t>
+          <t>$4201756  buc  2.0
+@ROBINET TRECERE LAVOAR DN 1/2"X1/2" COD 41R2718</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
@@ -2531,8 +2539,8 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>$4201756  buc  2.0
-@ROBINET TRECERE LAVOAR DN 1/2"X1/2" COD 41R2718</t>
+          <t>$3270494  buc  2.0
+RACORD FLEXIBIL &lt;WATERKIT&gt; D. 1/2"F-1/2"F L 60CM</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
@@ -2552,8 +2560,8 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>$3270494  buc  2.0
-RACORD FLEXIBIL &lt;WATERKIT&gt; D. 1/2"F-1/2"F L 60CM</t>
+          <t>SC12A#  buc  1.0
+ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
@@ -2573,8 +2581,8 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>SC12A#  buc  1.0
-ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
+          <t>$2451485  buc  1.0
+ETAJERE PORTELAN TIP E2.30 ALB C.1 NI</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -2594,8 +2602,8 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>$2451485  buc  1.0
-ETAJERE PORTELAN TIP E2.30 ALB C.1 NI</t>
+          <t>SC13A#  buc  1.0
+OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
@@ -2615,8 +2623,8 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>SC13A#  buc  1.0
-OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
+          <t>SC11A#  buc  1.0
+PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
@@ -2636,8 +2644,8 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>SC11A#  buc  1.0
-PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
+          <t>SC14A#  buc  1.0
+PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
@@ -2657,8 +2665,8 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>SC14A#  buc  1.0
-PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
+          <t>$2222226  buc  1.0
+SUPORT SAPUN INOX SI CERAMIC ALBA/STICLA MATA BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -2678,8 +2686,8 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>$2222226  buc  1.0
-SUPORT SAPUN INOX SI CERAMIC ALBA/STICLA MATA BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
+          <t>SC13A1  buc  4.0
+VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
         </is>
       </c>
       <c r="C111" s="8" t="inlineStr">
@@ -2699,8 +2707,8 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>SC13A1  buc  4.0
-VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
+          <t>$3272364  buc  4.0
+VAS WC SUSPENDAT UNIVERSAL</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -2720,8 +2728,8 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>$3272364  buc  4.0
-VAS WC SUSPENDAT UNIVERSAL</t>
+          <t>SC16G1  buc  4.0
+REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
         </is>
       </c>
       <c r="C113" s="8" t="inlineStr">
@@ -2741,8 +2749,8 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>SC16G1  buc  4.0
-REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
+          <t>SC18A5  buc  4.0
+RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -2762,8 +2770,8 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>SC18A5  buc  4.0
-RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
+          <t>SC30A2  buc  4.0
+SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
         </is>
       </c>
       <c r="C115" s="8" t="inlineStr">
@@ -2783,8 +2791,8 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>SC30A2  buc  4.0
-SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
+          <t>$2222212  buc  4.0
+SUPORT HARTIE IGIENICA INOX</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -2804,8 +2812,8 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>$2222212  buc  4.0
-SUPORT HARTIE IGIENICA INOX</t>
+          <t>SB17E1  buc  4.0
+COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
@@ -2825,8 +2833,8 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>SB17E1  buc  4.0
-COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
+          <t>$6701362  buc  4.0
+@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -2846,8 +2854,8 @@
       </c>
       <c r="B119" s="8" t="inlineStr">
         <is>
-          <t>$6701362  buc  4.0
-@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
+          <t>$2946036  buc  4.0
+robinet inox 1/2</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
@@ -2867,8 +2875,8 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>$2946036  buc  4.0
-robinet inox 1/2</t>
+          <t>$7341014  buc  4.0
+@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
@@ -2888,8 +2896,8 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>$7341014  buc  4.0
-@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
+          <t>$2222213  buc  4.0
+PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE BUC. MONTAT WC PERSOANE CU DIABILITATI - DESCRIERE:</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
@@ -2909,8 +2917,8 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>$2222213  buc  4.0
-PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE BUC. MONTAT WC PERSOANE CU DIABILITATI - DESCRIERE:</t>
+          <t>SC07A#  buc  1.0
+VAS CLOS, ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
@@ -2930,8 +2938,8 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>SC07A#  buc  1.0
-VAS CLOS, ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
+          <t>$2222214  buc  1.0
+VAS WC CU CAPAC SI REZERVOR CU BUTON ACTIONARE DUALA PENTRU PERSOANE DIZABILITATI</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
@@ -2951,8 +2959,8 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>$2222214  buc  1.0
-VAS WC CU CAPAC SI REZERVOR CU BUTON ACTIONARE DUALA PENTRU PERSOANE DIZABILITATI</t>
+          <t>$3275877  buc  1.0
+COT RACORD DN110 PT. WC</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
@@ -2972,8 +2980,8 @@
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t>$3275877  buc  1.0
-COT RACORD DN110 PT. WC</t>
+          <t>SD05A#  buc  1.0
+ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
@@ -2993,8 +3001,8 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>SD05A#  buc  1.0
-ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
+          <t>$3274252  buc  1.0
+RACORD FLEXIBIL 1/2" FE-FI 40 CM</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -3014,8 +3022,8 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>$3274252  buc  1.0
-RACORD FLEXIBIL 1/2" FE-FI 40 CM</t>
+          <t>SC30A5  buc  1.0
+SUPORT PT HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN TABLA DECAPATA TDA</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -3035,8 +3043,8 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>SC30A5  buc  1.0
-SUPORT PT HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN TABLA DECAPATA TDA</t>
+          <t>SC27A2  buc  1.0
+PORTPAHAR DIN FONTA, EMAILAT, SIMPLU</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
@@ -3056,8 +3064,8 @@
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t>SC27A2  buc  1.0
-PORTPAHAR DIN FONTA, EMAILAT, SIMPLU</t>
+          <t>SC29A1  buc  4.0
+CUIER PENTRU RUFARIE DIN FONTA EMAILATA, PORTELAN SANITAR SAU MATERIAL PLASTIC TIP</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -3077,8 +3085,8 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>SC29A1  buc  4.0
-CUIER PENTRU RUFARIE DIN FONTA EMAILATA, PORTELAN SANITAR SAU MATERIAL PLASTIC TIP</t>
+          <t>$6718879  buc  4.0
+CUIER BAIE AMINOPLAST 2 AGATATORI NI</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
@@ -3098,8 +3106,8 @@
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t>$6718879  buc  4.0
-CUIER BAIE AMINOPLAST 2 AGATATORI NI</t>
+          <t>SD04B1  buc  4.0
+BATERIE AMESTEC CU DUS FIX DE 1/2 TOLI, DIN FONTA SAU ALAMA, MONT CU DIBL LEMN PE ZID DE BETON</t>
         </is>
       </c>
       <c r="C131" s="8" t="inlineStr">
@@ -3119,8 +3127,8 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>SD04B1  buc  4.0
-BATERIE AMESTEC CU DUS FIX DE 1/2 TOLI, DIN FONTA SAU ALAMA, MONT CU DIBL LEMN PE ZID DE BETON</t>
+          <t>$3270746  buc  4.0
+BATERIE 8090 E CABINA DUS</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
@@ -3140,8 +3148,8 @@
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t>$3270746  buc  4.0
-BATERIE 8090 E CABINA DUS</t>
+          <t>SC03A1  buc  4.0
+CADA PENTRU DUS, CALIT.1, DIN FONTA EMAILATA PATRATA CU 1 .. . 2 LATURI LIBERE</t>
         </is>
       </c>
       <c r="C133" s="8" t="inlineStr">
@@ -3161,8 +3169,8 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>SC03A1  buc  4.0
-CADA PENTRU DUS, CALIT.1, DIN FONTA EMAILATA PATRATA CU 1 .. . 2 LATURI LIBERE</t>
+          <t>IZF17A1  mp  416.0
+TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
@@ -3182,8 +3190,8 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>IZF17A1  mp  416.0
-TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
+          <t>$3271283  mp  424.32
+VATA MINERALA BAZALTICA 10 CM</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
@@ -3203,8 +3211,8 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>$3271283  mp  424.32
-VATA MINERALA BAZALTICA 10 CM</t>
+          <t>CK26C1  buc  2496.0
+DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
@@ -3224,8 +3232,8 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>CK26C1  buc  2496.0
-DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
+          <t>$3274531  buc  3328.0
+DIBLURI DE POLISTIREN 150 MM</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -3245,8 +3253,8 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>$3274531  buc  3328.0
-DIBLURI DE POLISTIREN 150 MM</t>
+          <t>RPCE26C1  mp  416.0
+PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
@@ -3266,8 +3274,8 @@
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t>RPCE26C1  mp  416.0
-PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
+          <t>$3274536  mp  457.6
+PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
@@ -3287,8 +3295,8 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>$3274536  mp  457.6
-PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
+          <t>CF06B1  mp  416.0
+TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE VATA MIN. CU ADEZIV</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
@@ -3308,8 +3316,8 @@
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t>CF06B1  mp  416.0
-TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE VATA MIN. CU ADEZIV</t>
+          <t>$2101131  kg  3328.0
+@MORTAR ADEZIV PT PLACI TERMOIZOLANTE</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -3329,8 +3337,8 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>$2101131  kg  3328.0
-@MORTAR ADEZIV PT PLACI TERMOIZOLANTE</t>
+          <t>PF04A1  mp  416.0
+STRAT AMORSAJ APLICAT CU PERIA DIN BITUM</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
@@ -3350,8 +3358,8 @@
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t>PF04A1  mp  416.0
-STRAT AMORSAJ APLICAT CU PERIA DIN BITUM</t>
+          <t>$3274532  kg  62.4
+VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
@@ -3371,8 +3379,8 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>$3274532  kg  62.4
-VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
+          <t>CN06A1  mp  416.0
+VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
@@ -3392,8 +3400,8 @@
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t>CN06A1  mp  416.0
-VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
+          <t>$6104676  kg  1331.2
+VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
@@ -3413,8 +3421,8 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>$6104676  kg  1331.2
-VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
+          <t>CF24A1  mp  241.0
+PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
@@ -3434,8 +3442,8 @@
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t>CF24A1  mp  241.0
-PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
+          <t>$2100843  mp  0.0
+-250.640 @PLACA RB 12,5 MM</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
@@ -3455,8 +3463,8 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>$2100843  mp  0.0
--250.640 @PLACA RB 12,5 MM</t>
+          <t>$2100853  mp  250.64
+@PLACA RBI 12,5 MM</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
@@ -3476,8 +3484,8 @@
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t>$2100853  mp  250.64
-@PLACA RBI 12,5 MM</t>
+          <t>CF10C1  mp  241.0
+GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
@@ -3497,8 +3505,8 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>CF10C1  mp  241.0
-GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
+          <t>$3271744  buc  6.0
+COT PP D 110X45</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
@@ -3518,8 +3526,8 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>$3271744  buc  6.0
-COT PP D 110X45</t>
+          <t>$3271713  buc  18.0
+COT PP 32X45</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
@@ -3539,8 +3547,8 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>$3271713  buc  18.0
-COT PP 32X45</t>
+          <t>$3271714  buc  28.0
+COT PP 40X45</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
@@ -3560,8 +3568,8 @@
       </c>
       <c r="B153" s="8" t="inlineStr">
         <is>
-          <t>$3271714  buc  28.0
-COT PP 40X45</t>
+          <t>SF03A1  m  120.0
+EFECTUARE PROBA DE ETANS. LA PRES.A INST. INTR.DE APA, DIN TEVI PVC MONT. IN CANAL. INCLUSIV ARMATU</t>
         </is>
       </c>
       <c r="C153" s="8" t="inlineStr">
@@ -3581,8 +3589,8 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>SF03A1  m  120.0
-EFECTUARE PROBA DE ETANS. LA PRES.A INST. INTR.DE APA, DIN TEVI PVC MONT. IN CANAL. INCLUSIV ARMATU</t>
+          <t>SE17E1  buc  6.0
+GRATAR PENTRU FRIPT, CU PLACI RADIANTE, DE 1030X660X800MM, FUNCT.CU GAZE</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
@@ -3602,8 +3610,8 @@
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t>SE17E1  buc  6.0
-GRATAR PENTRU FRIPT, CU PLACI RADIANTE, DE 1030X660X800MM, FUNCT.CU GAZE</t>
+          <t>$2992112  buc  6.0
+RIGOLE DUS INOX BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C155" s="8" t="inlineStr">
@@ -3623,8 +3631,8 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>$2992112  buc  6.0
-RIGOLE DUS INOX BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
+          <t>SC07A1  buc  9.0
+LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
@@ -3644,8 +3652,8 @@
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t>SC07A1  buc  9.0
-LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
+          <t>$2438407  buc  9.0
+LAVOAR PORTELAN F. SPATAR L12-630MM ALB C. 2 N1080</t>
         </is>
       </c>
       <c r="C157" s="8" t="inlineStr">
@@ -3665,8 +3673,8 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>$2438407  buc  9.0
-LAVOAR PORTELAN F. SPATAR L12-630MM ALB C. 2 N1080</t>
+          <t>SC19B1  buc  9.0
+SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
@@ -3686,8 +3694,8 @@
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>SC19B1  buc  9.0
-SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
+          <t>$4202797  buc  9.0
+SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
         </is>
       </c>
       <c r="C159" s="8" t="inlineStr">
@@ -3707,8 +3715,8 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>$4202797  buc  9.0
-SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
+          <t>SC25A1  buc  9.0
+ETAJERA DIN PORTELAN SANITAR TIP</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
@@ -3728,8 +3736,8 @@
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t>SC25A1  buc  9.0
-ETAJERA DIN PORTELAN SANITAR TIP</t>
+          <t>$2451875  buc  9.0
+ETAJERA PORTELAN TIP E2.60 ALB C.2 NI</t>
         </is>
       </c>
       <c r="C161" s="8" t="inlineStr">
@@ -3749,8 +3757,8 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>$2451875  buc  9.0
-ETAJERA PORTELAN TIP E2.60 ALB C.2 NI</t>
+          <t>SC26A1  buc  9.0
+OGLINDA SANIT. SEMICRIST.MARGINI . SLEF.CU DIMENS . 400X500MM</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
@@ -3770,8 +3778,8 @@
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t>SC26A1  buc  9.0
-OGLINDA SANIT. SEMICRIST.MARGINI . SLEF.CU DIMENS . 400X500MM</t>
+          <t>$2222224  buc  9.0
+OGLINDA CU RAMA ALUMINIU</t>
         </is>
       </c>
       <c r="C163" s="8" t="inlineStr">
@@ -3791,8 +3799,8 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>$2222224  buc  9.0
-OGLINDA CU RAMA ALUMINIU</t>
+          <t>SC31A1  buc  9.0
+VENTIL DE SCURGERE TIP</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
@@ -3812,8 +3820,8 @@
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t>SC31A1  buc  9.0
-VENTIL DE SCURGERE TIP</t>
+          <t>$4203179  buc  9.0
+VENTIL SCURGERE LAVOAR, BIDEU 1 1/4"""" FARA RACORD S 411</t>
         </is>
       </c>
       <c r="C165" s="8" t="inlineStr">
@@ -3833,8 +3841,8 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>$4203179  buc  9.0
-VENTIL SCURGERE LAVOAR, BIDEU 1 1/4"""" FARA RACORD S 411</t>
+          <t>SD06A1  buc  9.0
+BATERIE AMESTECATOARE, STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
@@ -3854,8 +3862,8 @@
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>SD06A1  buc  9.0
-BATERIE AMESTECATOARE, STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
+          <t>$3272003  buc  9.0
+BATERIE MONOCOMANDA PENTRU LAVOAR</t>
         </is>
       </c>
       <c r="C167" s="8" t="inlineStr">
@@ -3875,8 +3883,8 @@
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>$3272003  buc  9.0
-BATERIE MONOCOMANDA PENTRU LAVOAR</t>
+          <t>SD12A1  buc  18.0
+ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
@@ -3896,8 +3904,8 @@
       </c>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>SD12A1  buc  18.0
-ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
+          <t>$4201779  buc  18.0
+ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
         </is>
       </c>
       <c r="C169" s="8" t="inlineStr">
@@ -3917,8 +3925,8 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>$4201779  buc  18.0
-ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
+          <t>SC28B1  buc  9.0
+SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
@@ -3938,8 +3946,8 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>SC28B1  buc  9.0
-SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
+          <t>$2222225  buc  9.0
+DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
         </is>
       </c>
       <c r="C171" s="8" t="inlineStr">
@@ -3959,8 +3967,8 @@
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>$2222225  buc  9.0
-DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
+          <t>SC24A1  buc  9.0
+PORTPROSOP DIN AM NICHEL. MONT. PE PERETI TIP U, CU 1 BRAT, DESCHID. 450MM</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
@@ -3980,8 +3988,8 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>SC24A1  buc  9.0
-PORTPROSOP DIN AM NICHEL. MONT. PE PERETI TIP U, CU 1 BRAT, DESCHID. 450MM</t>
+          <t>$2222227  buc  9.0
+DISPENSER INOX SERVETELE HARTIE BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C173" s="8" t="inlineStr">
@@ -4001,8 +4009,8 @@
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>$2222227  buc  9.0
-DISPENSER INOX SERVETELE HARTIE BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
+          <t>SC13A1  buc  7.0
+VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
@@ -4022,8 +4030,8 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>SC13A1  buc  7.0
-VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
+          <t>$3272364  buc  7.0
+VAS WC SUSPENDAT UNIVERSAL</t>
         </is>
       </c>
       <c r="C175" s="8" t="inlineStr">
@@ -4043,8 +4051,8 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>$3272364  buc  7.0
-VAS WC SUSPENDAT UNIVERSAL</t>
+          <t>SC16G1  buc  7.0
+REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
@@ -4064,8 +4072,8 @@
       </c>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>SC16G1  buc  7.0
-REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
+          <t>SC18A5  buc  7.0
+RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
         </is>
       </c>
       <c r="C177" s="8" t="inlineStr">
@@ -4085,8 +4093,8 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>SC18A5  buc  7.0
-RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
+          <t>SC30A2  buc  7.0
+SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
@@ -4106,8 +4114,8 @@
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>SC30A2  buc  7.0
-SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
+          <t>$2222212  buc  7.0
+SUPORT HARTIE IGIENICA INOX</t>
         </is>
       </c>
       <c r="C179" s="8" t="inlineStr">
@@ -4127,8 +4135,8 @@
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>$2222212  buc  7.0
-SUPORT HARTIE IGIENICA INOX</t>
+          <t>SB17E1  buc  7.0
+COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
@@ -4148,8 +4156,8 @@
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t>SB17E1  buc  7.0
-COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
+          <t>$6701362  buc  7.0
+@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
         </is>
       </c>
       <c r="C181" s="8" t="inlineStr">
@@ -4169,8 +4177,8 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>$6701362  buc  7.0
-@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
+          <t>$2946036  buc  7.0
+robinet inox 1/2</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
@@ -4190,8 +4198,8 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>$2946036  buc  7.0
-robinet inox 1/2</t>
+          <t>$7341014  buc  7.0
+@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
         </is>
       </c>
       <c r="C183" s="8" t="inlineStr">
@@ -4211,8 +4219,8 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>$7341014  buc  7.0
-@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
+          <t>$2222213  buc  7.0
+PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
@@ -4232,8 +4240,8 @@
       </c>
       <c r="B185" s="8" t="inlineStr">
         <is>
-          <t>$2222213  buc  7.0
-PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE</t>
+          <t>SD02A#  buc  14.0
+BATERIE BAIE AMESTEC, CU DUS FLEX SAU FIX, INDIF INCHID, INCL PT HAND, MOBT PE PERETI CARAM SAU BCA</t>
         </is>
       </c>
       <c r="C185" s="8" t="inlineStr">
@@ -4253,8 +4261,8 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>SD02A#  buc  14.0
-BATERIE BAIE AMESTEC, CU DUS FLEX SAU FIX, INDIF INCHID, INCL PT HAND, MOBT PE PERETI CARAM SAU BCA</t>
+          <t>$6705000  buc  14.0
+SISTEM DE DUS, INCLUDE BATERIE DUS, COLOANA DUS SI MATERIALE DE MONTAJ BUC. MONTAT DUS GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
@@ -4274,8 +4282,8 @@
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>$6705000  buc  14.0
-SISTEM DE DUS, INCLUDE BATERIE DUS, COLOANA DUS SI MATERIALE DE MONTAJ BUC. MONTAT DUS GRUP SANITAR - DESCRIERE:</t>
+          <t>SC29A1  buc  3.0
+CUIER PENTRU RUFARIE DIN FONTA EMAILATA, PORTELAN SANITAR SAU MATERIAL PLASTIC TIP</t>
         </is>
       </c>
       <c r="C187" s="8" t="inlineStr">
@@ -4295,8 +4303,8 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>SC29A1  buc  3.0
-CUIER PENTRU RUFARIE DIN FONTA EMAILATA, PORTELAN SANITAR SAU MATERIAL PLASTIC TIP</t>
+          <t>$6718879  buc  3.0
+CUIER BAIE AMINOPLAST 2 AGATATORI NI</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
@@ -4316,8 +4324,8 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>$6718879  buc  3.0
-CUIER BAIE AMINOPLAST 2 AGATATORI NI</t>
+          <t>SD04B1  buc  3.0
+BATERIE AMESTEC CU DUS FIX DE 1/2 TOLI, DIN FONTA SAU ALAMA, MONT CU DIBL LEMN PE ZID DE BETON</t>
         </is>
       </c>
       <c r="C189" s="8" t="inlineStr">
@@ -4337,8 +4345,8 @@
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>SD04B1  buc  3.0
-BATERIE AMESTEC CU DUS FIX DE 1/2 TOLI, DIN FONTA SAU ALAMA, MONT CU DIBL LEMN PE ZID DE BETON</t>
+          <t>$3270746  buc  3.0
+BATERIE 8090 E CABINA DUS</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
@@ -4358,8 +4366,8 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>$3270746  buc  3.0
-BATERIE 8090 E CABINA DUS</t>
+          <t>SC03A1  buc  3.0
+CADA PENTRU DUS, CALIT.1, DIN FONTA EMAILATA PATRATA CU 1 ... 2 LATURI LIBERE</t>
         </is>
       </c>
       <c r="C191" s="8" t="inlineStr">
@@ -4379,8 +4387,8 @@
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>SC03A1  buc  3.0
-CADA PENTRU DUS, CALIT.1, DIN FONTA EMAILATA PATRATA CU 1 ... 2 LATURI LIBERE</t>
+          <t>CF06B1  mp  120.0
+TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE ZIDURI, IN GROSIME MEDIE DE 2,5CM</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
@@ -4400,8 +4408,8 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>CF06B1  mp  120.0
-TENCUIELI EXTERIOARE OBISNUITE, DRISCUITE PE ZIDURI, IN GROSIME MEDIE DE 2,5CM</t>
+          <t>IZF17A1  mp  120.0
+TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
         </is>
       </c>
       <c r="C193" s="8" t="inlineStr">
@@ -4421,8 +4429,8 @@
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>IZF17A1  mp  120.0
-TERMOIZOLATIE PERETI NTE DIN VATA MINERALA MONTATE CU PIESE METAL DE SUSTINER</t>
+          <t>$3271283  mp  122.4
+VATA MINERALA BAZALTICA 40 KG/M3 , 10 CM 1 BAX=2, 4M2</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
@@ -4442,8 +4450,8 @@
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>$3271283  mp  122.4
-VATA MINERALA BAZALTICA 40 KG/M3 , 10 CM 1 BAX=2, 4M2</t>
+          <t>CK26C1  buc  720.0
+DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
         </is>
       </c>
       <c r="C195" s="8" t="inlineStr">
@@ -4463,8 +4471,8 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>CK26C1  buc  720.0
-DIBLURI METALICE IMPUSCATE IN PLANSEE SAU PERETI DIN BETON ARMAT</t>
+          <t>$3274531  buc  960.0
+DIBLURI DE POLISTIREN 150 MM</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
@@ -4484,8 +4492,8 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>$3274531  buc  960.0
-DIBLURI DE POLISTIREN 150 MM</t>
+          <t>RPCE26C1  mp  120.0
+PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
         </is>
       </c>
       <c r="C197" s="8" t="inlineStr">
@@ -4505,8 +4513,8 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>RPCE26C1  mp  120.0
-PLASA RABIT ZN.MONT. LA PERETI FIXATI PE IZ. IN VEDEREA TEN</t>
+          <t>$3274536  mp  132.0
+PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
@@ -4526,8 +4534,8 @@
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>$3274536  mp  132.0
-PLASA DIN FIBRA DE STICLA PENTRU POLISTIREN</t>
+          <t>$2101131  kg  960.0
+@MORTAR ADEZIV PT PLACI TERMOIZOLANTE MP. VOPSITORII DECORATIVA - DESCRIERE:</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
@@ -4547,8 +4555,8 @@
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>$2101131  kg  960.0
-@MORTAR ADEZIV PT PLACI TERMOIZOLANTE MP. VOPSITORII DECORATIVA - DESCRIERE:</t>
+          <t>PF04A1  mp  120.0
+STRAT AMORSAJ APLICAT CU PERIA DIN BITUM TAIAT CU WHITE SPIRIT RAFINAT</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
@@ -4568,8 +4576,8 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>PF04A1  mp  120.0
-STRAT AMORSAJ APLICAT CU PERIA DIN BITUM TAIAT CU WHITE SPIRIT RAFINAT</t>
+          <t>$3274532  kg  18.0
+VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
@@ -4589,8 +4597,8 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>$3274532  kg  18.0
-VOPSEA GRUND PENTRU PREGATIREA SUPORTULUI INAINTEA APLICARII TENCUIELII DECORATIVE ALBE GALEATA 12KG</t>
+          <t>CN06A1  mp  120.0
+VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
@@ -4610,8 +4618,8 @@
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>CN06A1  mp  120.0
-VOPSITORII DECORATIVE IN RELIEF, APLICATE IN DOUA STRATURI DE VOPSEA DECORATIVA</t>
+          <t>$6104676  kg  384.0
+VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
@@ -4631,8 +4639,8 @@
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>$6104676  kg  384.0
-VOPSEA EFECT DECORATIV CU PASTA SR. 8203- 2B NTR 4741-71</t>
+          <t>CF24A1  mp  24.0
+PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
@@ -4652,8 +4660,8 @@
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>CF24A1  mp  24.0
-PLAFON FIX RIGIPS CU STRUCTURA METALICA</t>
+          <t>$2100843  mp  0.0
+-24.960 @PLACA RB 12,5 MM</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
@@ -4673,8 +4681,8 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>$2100843  mp  0.0
--24.960 @PLACA RB 12,5 MM</t>
+          <t>$2100853  mp  24.96
+@PLACA RBI 12,5 MM</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
@@ -4694,8 +4702,8 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>$2100853  mp  24.96
-@PLACA RBI 12,5 MM</t>
+          <t>CF10C1  mp  24.0
+GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
         </is>
       </c>
       <c r="C207" s="8" t="inlineStr">
@@ -4715,8 +4723,8 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>CF10C1  mp  24.0
-GLET DE IPSOS APLICAT LA TENCUIELI INTERIOARE DRISCUITE</t>
+          <t>$3270156  kg  2.4
+AMORSA PENTRU VOPSEA LAVABILA</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
@@ -4736,8 +4744,8 @@
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>$3270156  kg  2.4
-AMORSA PENTRU VOPSEA LAVABILA</t>
+          <t>RPCR21A#  mp  24.0
+Vopsitorii interioare cu vopsea lavabila la pereti si tavane cu vopsea lavabila, pe glet de ipsos</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr">
@@ -4757,8 +4765,8 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>RPCR21A#  mp  24.0
-Vopsitorii interioare cu vopsea lavabila la pereti si tavane cu vopsea lavabila, pe glet de ipsos</t>
+          <t>CG01D1  mp  49.0
+STRAT SUPORT PT. PARDOSELI EXECUTATE DIN MORTAR DE CIMENT M100-T 10CM GROSIME</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
@@ -4778,8 +4786,8 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>CG01D1  mp  49.0
-STRAT SUPORT PT. PARDOSELI EXECUTATE DIN MORTAR DE CIMENT M100-T 10CM GROSIME</t>
+          <t>SF02A1  m  46.0
+EFECTUARE PROBA DE ETANS . LA PRES.A INST. INTER. DE APA, EXECUTATE CU TEVI PVC INCLUSIV ARMATURILE</t>
         </is>
       </c>
       <c r="C211" s="8" t="inlineStr">
@@ -4799,8 +4807,8 @@
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>SF02A1  m  46.0
-EFECTUARE PROBA DE ETANS . LA PRES.A INST. INTER. DE APA, EXECUTATE CU TEVI PVC INCLUSIV ARMATURILE</t>
+          <t>SF05C#  m  46.0
+SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
@@ -4820,8 +4828,8 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>SF05C#  m  46.0
-SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
+          <t>SB09E#  buc  4.0
+PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=110MM</t>
         </is>
       </c>
       <c r="C213" s="8" t="inlineStr">
@@ -4841,8 +4849,8 @@
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t>SB09E#  buc  4.0
-PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=110MM</t>
+          <t>$3274797  buc  2.0
+REDUCTIE EXCENTRICA 110/50 /TEVI SI FITINGURI PP IGNIFUGATE CU GARNITURA PENTRU RETELE DE SCURGERI INTERIOARE SI TEVI DIN PVC</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
@@ -4862,8 +4870,8 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>$3274797  buc  2.0
-REDUCTIE EXCENTRICA 110/50 /TEVI SI FITINGURI PP IGNIFUGATE CU GARNITURA PENTRU RETELE DE SCURGERI INTERIOARE SI TEVI DIN PVC</t>
+          <t>$3272973  buc  4.0
+COT 110,45 GRADE PP</t>
         </is>
       </c>
       <c r="C215" s="8" t="inlineStr">
@@ -4883,8 +4891,8 @@
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>$3272973  buc  4.0
-COT 110,45 GRADE PP</t>
+          <t>$3271421  buc  1.0
+RAMIFICATIE 110/110/45 BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
@@ -4904,8 +4912,8 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>$3271421  buc  1.0
-RAMIFICATIE 110/110/45 BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
+          <t>SC07A1  buc  4.0
+LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
         </is>
       </c>
       <c r="C217" s="8" t="inlineStr">
@@ -4925,8 +4933,8 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>SC07A1  buc  4.0
-LAVOAR DIN PORTELAN SANITAR, MONTAT PE CONSOLE FIXATE CU DIBLURI DE LEMN PE ZID DE CARAMIDA</t>
+          <t>$2438407  buc  4.0
+LAVOAR PORTELAN</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
@@ -4946,8 +4954,8 @@
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>$2438407  buc  4.0
-LAVOAR PORTELAN</t>
+          <t>SC19B1  buc  4.0
+SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
         </is>
       </c>
       <c r="C219" s="8" t="inlineStr">
@@ -4967,8 +4975,8 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>SC19B1  buc  4.0
-SIFON DIN FONTA SAU TEAVA DE ALAMA PT. LAVOAR DE PORTELAN SANITAR</t>
+          <t>$4202797  buc  4.0
+SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
@@ -4988,8 +4996,8 @@
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>$4202797  buc  4.0
-SIFON PENTRU LAVOAR TIP BUTELIE ALAMA 1 1/4"" S 9611</t>
+          <t>SC25A1  buc  4.0
+ETAJERA DIN PORTELAN SANITAR TIP</t>
         </is>
       </c>
       <c r="C221" s="8" t="inlineStr">
@@ -5009,8 +5017,8 @@
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>SC25A1  buc  4.0
-ETAJERA DIN PORTELAN SANITAR TIP</t>
+          <t>$2451875  buc  4.0
+ETAJERA</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
@@ -5030,8 +5038,8 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>$2451875  buc  4.0
-ETAJERA</t>
+          <t>SC26A1  buc  4.0
+OGLINDA SANIT. SEMICRIST.MARGINI.SLEF.CU DIMENS . 400X500MM</t>
         </is>
       </c>
       <c r="C223" s="8" t="inlineStr">
@@ -5051,8 +5059,8 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>SC26A1  buc  4.0
-OGLINDA SANIT. SEMICRIST.MARGINI.SLEF.CU DIMENS . 400X500MM</t>
+          <t>$2222224  buc  4.0
+OGLINDA</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
@@ -5072,8 +5080,8 @@
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>$2222224  buc  4.0
-OGLINDA</t>
+          <t>SC31A1  buc  4.0
+VENTIL DE SCURGERE TIP</t>
         </is>
       </c>
       <c r="C225" s="8" t="inlineStr">
@@ -5093,8 +5101,8 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>SC31A1  buc  4.0
-VENTIL DE SCURGERE TIP</t>
+          <t>$4203179  buc  4.0
+VENTIL SCURGERE LAVOAR, BIDEU 1 1/4"""" FARA RACORD S 411</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
@@ -5114,8 +5122,8 @@
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>$4203179  buc  4.0
-VENTIL SCURGERE LAVOAR, BIDEU 1 1/4"""" FARA RACORD S 411</t>
+          <t>SD06A1  buc  4.0
+BATERIE AMESTECATOARE , STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C227" s="8" t="inlineStr">
@@ -5135,8 +5143,8 @@
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>SD06A1  buc  4.0
-BATERIE AMESTECATOARE , STATIVA, PENTRU LAVOAR AVIND D=1/2 TOLI</t>
+          <t>$3272003  buc  4.0
+BATERIE MONOCOMANDA PENTRU LAVOAR</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
@@ -5156,8 +5164,8 @@
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>$3272003  buc  4.0
-BATERIE MONOCOMANDA PENTRU LAVOAR</t>
+          <t>SD12A1  buc  8.0
+ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
         </is>
       </c>
       <c r="C229" s="8" t="inlineStr">
@@ -5177,8 +5185,8 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>SD12A1  buc  8.0
-ROBINET DE REGLAJ, DE COLT, DIN ALAMA NICHELATA, AVIND D=3/8 SAU D=1/2 TOLI</t>
+          <t>$4201779  buc  8.0
+ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
@@ -5198,8 +5206,8 @@
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>$4201779  buc  8.0
-ROBINET COLT REGLAJ ALAMA NICHELATA 1/2 "" S 751/I</t>
+          <t>SC28B1  buc  4.0
+SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
         </is>
       </c>
       <c r="C231" s="8" t="inlineStr">
@@ -5219,8 +5227,8 @@
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>SC28B1  buc  4.0
-SAPUNIERA DIN PORTELAN SANITAR, TIP SA2- 15, APARENTA, SIMPLA</t>
+          <t>$2222225  buc  4.0
+DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
@@ -5240,8 +5248,8 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>$2222225  buc  4.0
-DOZATOR SAPUN LIVHID DIN INOX 500-700 ML</t>
+          <t>SC24A1  buc  4.0
+PORTPROSOP DIN AM NICHEL. MONT. PE PERETI TIP U, CU 1 BRAT, DESCHID. 450MM</t>
         </is>
       </c>
       <c r="C233" s="8" t="inlineStr">
@@ -5261,8 +5269,8 @@
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>SC24A1  buc  4.0
-PORTPROSOP DIN AM NICHEL. MONT. PE PERETI TIP U, CU 1 BRAT, DESCHID. 450MM</t>
+          <t>$2222227  buc  4.0
+DISPENSER INOX SERVETELE HARTIE BUC. MONTAT LAVOAR PERSOANE CU DIZABIL</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
@@ -5282,8 +5290,8 @@
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>$2222227  buc  4.0
-DISPENSER INOX SERVETELE HARTIE BUC. MONTAT LAVOAR PERSOANE CU DIZABIL</t>
+          <t>SC04A#  buc  1.0
+LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
         </is>
       </c>
       <c r="C235" s="8" t="inlineStr">
@@ -5303,8 +5311,8 @@
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>SC04A#  buc  1.0
-LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
+          <t>$2222215  buc  1.0
+LAVOAR PERSOANE CU DISABILITATI</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
@@ -5324,8 +5332,8 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>$2222215  buc  1.0
-LAVOAR PERSOANE CU DISABILITATI</t>
+          <t>TCC18C1  buc  1.0
+DISPOZITIV DE MONTARE A GHIDULUI DE UNDA: CONSOLA MONTARE</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
@@ -5345,8 +5353,8 @@
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>TCC18C1  buc  1.0
-DISPOZITIV DE MONTARE A GHIDULUI DE UNDA: CONSOLA MONTARE</t>
+          <t>$2222217  buc  1.0
+BARA SPRIJINI PERSOANE CU DIZABILITATI</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
@@ -5366,8 +5374,8 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>$2222217  buc  1.0
-BARA SPRIJINI PERSOANE CU DIZABILITATI</t>
+          <t>SD04A#  buc  1.0
+BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
         </is>
       </c>
       <c r="C239" s="8" t="inlineStr">
@@ -5387,8 +5395,8 @@
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>SD04A#  buc  1.0
-BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
+          <t>$2222216  buc  1.0
+BATERIE LAVOAR PERSOANE CU DISABILITATI</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
@@ -5408,8 +5416,8 @@
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>$2222216  buc  1.0
-BATERIE LAVOAR PERSOANE CU DISABILITATI</t>
+          <t>$4203301  buc  1.0
+VENTIL SCURGERE LAVOAR, SPALATOR 1"" FARA RACORD S9610</t>
         </is>
       </c>
       <c r="C241" s="8" t="inlineStr">
@@ -5429,8 +5437,8 @@
       </c>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>$4203301  buc  1.0
-VENTIL SCURGERE LAVOAR, SPALATOR 1"" FARA RACORD S9610</t>
+          <t>$4202761  buc  1.0
+SIFON ALAMA PENTRU LAVOAR 1"" S 9611</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
@@ -5450,8 +5458,8 @@
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>$4202761  buc  1.0
-SIFON ALAMA PENTRU LAVOAR 1"" S 9611</t>
+          <t>SD05A1  buc  2.0
+ROBINET PENTRU LAVOAR TIP AVIND DIAMETRUL DE 1/2 TOLI</t>
         </is>
       </c>
       <c r="C243" s="8" t="inlineStr">
@@ -5471,8 +5479,8 @@
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>SD05A1  buc  2.0
-ROBINET PENTRU LAVOAR TIP AVIND DIAMETRUL DE 1/2 TOLI</t>
+          <t>$4201756  buc  2.0
+@ROBINET TRECERE LAVOAR DN 1/2"X1/2" COD 41R2718</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
@@ -5492,8 +5500,8 @@
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>$4201756  buc  2.0
-@ROBINET TRECERE LAVOAR DN 1/2"X1/2" COD 41R2718</t>
+          <t>$3270494  buc  2.0
+RACORD FLEXIBIL &lt;WATERKIT&gt; D. 1/2"F-1/2"F L 60CM</t>
         </is>
       </c>
       <c r="C245" s="8" t="inlineStr">
@@ -5513,8 +5521,8 @@
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t>$3270494  buc  2.0
-RACORD FLEXIBIL &lt;WATERKIT&gt; D. 1/2"F-1/2"F L 60CM</t>
+          <t>SC12A#  buc  1.0
+ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
@@ -5534,8 +5542,8 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>SC12A#  buc  1.0
-ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
+          <t>$2451485  buc  1.0
+ETAJERE PORTELAN TIP E2.30 ALB C.1 NI</t>
         </is>
       </c>
       <c r="C247" s="8" t="inlineStr">
@@ -5555,8 +5563,8 @@
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>$2451485  buc  1.0
-ETAJERE PORTELAN TIP E2.30 ALB C.1 NI</t>
+          <t>SC13A#  buc  1.0
+OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
@@ -5576,8 +5584,8 @@
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>SC13A#  buc  1.0
-OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
+          <t>SC11A#  buc  1.0
+PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
         </is>
       </c>
       <c r="C249" s="8" t="inlineStr">
@@ -5597,8 +5605,8 @@
       </c>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>SC11A#  buc  1.0
-PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
+          <t>SC14A#  buc  1.0
+PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
@@ -5618,8 +5626,8 @@
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>SC14A#  buc  1.0
-PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
+          <t>$2222226  buc  1.0
+SUPORT SAPUN INOX SI CERAMIC ALBA/STICLA MATA BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
       <c r="C251" s="8" t="inlineStr">
@@ -5639,8 +5647,8 @@
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>$2222226  buc  1.0
-SUPORT SAPUN INOX SI CERAMIC ALBA/STICLA MATA BUC. MONTAT WC GRUP SANITAR - DESCRIERE:</t>
+          <t>SC13A1  buc  4.0
+VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
@@ -5660,8 +5668,8 @@
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>SC13A1  buc  4.0
-VAS PENTRU CLOSET DIN PORTELAN SANITAR CU SIFON INTERIOR S TIP</t>
+          <t>$3272364  buc  4.0
+VAS WC</t>
         </is>
       </c>
       <c r="C253" s="8" t="inlineStr">
@@ -5681,8 +5689,8 @@
       </c>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>$3272364  buc  4.0
-VAS WC</t>
+          <t>SC16G1  buc  4.0
+REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
@@ -5702,8 +5710,8 @@
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>SC16G1  buc  4.0
-REZERVOR PT SPALARE VAS WC, DIN PORTELAN TIP DUOBLOC, MONTAT PE VAS</t>
+          <t>SC18A5  buc  4.0
+RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
         </is>
       </c>
       <c r="C255" s="8" t="inlineStr">
@@ -5723,8 +5731,8 @@
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>SC18A5  buc  4.0
-RAMA PENTRU VAS DE CLOSET, DIN POLIPROPILENA CU CAPAC</t>
+          <t>SC30A2  buc  4.0
+SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
@@ -5744,8 +5752,8 @@
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>SC30A2  buc  4.0
-SUPORT PT. HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN PORTELAN SANITAR, HI 1</t>
+          <t>$2222212  buc  4.0
+SUPORT HARTIE IGIENICA</t>
         </is>
       </c>
       <c r="C257" s="8" t="inlineStr">
@@ -5765,8 +5773,8 @@
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>$2222212  buc  4.0
-SUPORT HARTIE IGIENICA</t>
+          <t>SB17E1  buc  4.0
+COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
@@ -5786,8 +5794,8 @@
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>SB17E1  buc  4.0
-COTURI PVC-U, PT. CANALIZARE, CU IMBINARE PRIN LIPIRELA 45;67 1/2;87 1/2 GRADE, AVIND D=110 MM</t>
+          <t>$6701362  buc  4.0
+@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
         </is>
       </c>
       <c r="C259" s="8" t="inlineStr">
@@ -5807,8 +5815,8 @@
       </c>
       <c r="B260" s="8" t="inlineStr">
         <is>
-          <t>$6701362  buc  4.0
-@COT RACORD WC ORIENTABIL 0-90 GR DN110 COD 62608001</t>
+          <t>$2946036  buc  4.0
+robinet inox 1/2</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
@@ -5828,8 +5836,8 @@
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>$2946036  buc  4.0
-robinet inox 1/2</t>
+          <t>$7341014  buc  4.0
+@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
         </is>
       </c>
       <c r="C261" s="8" t="inlineStr">
@@ -5849,8 +5857,8 @@
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>$7341014  buc  4.0
-@RACORD FLEXIBIL DN1/2X3/8FF L=30 CM COD</t>
+          <t>$2222213  buc  4.0
+PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE BUC. MONTAT WC PERSOANE CU DIABILITATI - DESCRIERE:</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
@@ -5870,8 +5878,8 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>$2222213  buc  4.0
-PERIE WC SI SUPORT INOX/STICLA MATA, SUSPENDAT DE PERETE BUC. MONTAT WC PERSOANE CU DIABILITATI - DESCRIERE:</t>
+          <t>SC07A#  buc  1.0
+VAS CLOS , ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
         </is>
       </c>
       <c r="C263" s="8" t="inlineStr">
@@ -5891,8 +5899,8 @@
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>SC07A#  buc  1.0
-VAS CLOS , ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
+          <t>$2222214  buc  1.0
+VAS WC CU CAPAC SI REZERVOR CU BUTON ACTIONARE DUALA PENTRU PERSOANE DIZABILITATI</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
@@ -5912,8 +5920,8 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>$2222214  buc  1.0
-VAS WC CU CAPAC SI REZERVOR CU BUTON ACTIONARE DUALA PENTRU PERSOANE DIZABILITATI</t>
+          <t>$3275877  buc  1.0
+COT RACORD DN110 PT. WC</t>
         </is>
       </c>
       <c r="C265" s="8" t="inlineStr">
@@ -5933,8 +5941,8 @@
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>$3275877  buc  1.0
-COT RACORD DN110 PT. WC</t>
+          <t>SD05A#  buc  1.0
+ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
@@ -5954,8 +5962,8 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>SD05A#  buc  1.0
-ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
+          <t>$3274252  buc  1.0
+RACORD FLEXIBIL 1/2" FE-FI 40 CM</t>
         </is>
       </c>
       <c r="C267" s="8" t="inlineStr">
@@ -5975,8 +5983,8 @@
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>$3274252  buc  1.0
-RACORD FLEXIBIL 1/2" FE-FI 40 CM</t>
+          <t>SC30A5  buc  1.0
+SUPORT PT HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN TABLA DECAPATA TDA</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
@@ -5996,74 +6004,74 @@
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>SC30A5  buc  1.0
-SUPORT PT HIRTIE CALITATEA 1 (PORTHIRTIE ) DIN TABLA DECAPATA TDA</t>
-        </is>
-      </c>
-      <c r="C269" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D269" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="40" customHeight="1">
-      <c r="A270" s="7" t="n">
-        <v>255</v>
-      </c>
-      <c r="B270" s="8" t="inlineStr">
-        <is>
           <t>SC27A2  buc  1.0
 PORTPAHAR DIN FONTA, EMAILAT, SIMPLU</t>
         </is>
       </c>
-      <c r="C270" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="6" t="inlineStr">
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: MONTAT BOILER OB.2</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="40" customHeight="1">
-      <c r="A272" s="7" t="n">
-        <v>256</v>
-      </c>
-      <c r="B272" s="8" t="inlineStr">
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="7" t="n">
+        <v>255</v>
+      </c>
+      <c r="B271" s="8" t="inlineStr">
         <is>
           <t>IA22C1  buc  2.0
 MONTARE BOILER GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Din care: Valoare aferenta utilaje termice = Valoare aferenta utilaje electrice = GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024 PROIECTANT S.C. DESIGN STUDIO SRL Patisce OVISTE . DAMSOVIT</t>
         </is>
       </c>
-      <c r="C272" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D272" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="20" customHeight="1">
-      <c r="A273" s="6" t="inlineStr">
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: INSTALATII VENTILATIE OB.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" s="7" t="n">
+        <v>256</v>
+      </c>
+      <c r="B273" s="8" t="inlineStr">
+        <is>
+          <t>VC01C1  buc  4.0
+MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
+        </is>
+      </c>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6073,8 +6081,8 @@
       </c>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>VC01C1  buc  4.0
-MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
+          <t>$3270546  buc  4.0
+VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
@@ -6094,8 +6102,8 @@
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>$3270546  buc  4.0
-VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
+          <t>VB14D1  buc  4.0
+PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
         </is>
       </c>
       <c r="C275" s="8" t="inlineStr">
@@ -6115,8 +6123,8 @@
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>VB14D1  buc  4.0
-PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
+          <t>$7002221  buc  4.0
+GRILA VENTILATIE DN110 MM</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
@@ -6136,8 +6144,8 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>$7002221  buc  4.0
-GRILA VENTILATIE DN110 MM</t>
+          <t>VB30A1  buc  4.0
+ANEMOSTAT PLAN PATRAT DET TIP 61/272</t>
         </is>
       </c>
       <c r="C277" s="8" t="inlineStr">
@@ -6157,8 +6165,8 @@
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>VB30A1  buc  4.0
-ANEMOSTAT PLAN PATRAT DET TIP 61/272</t>
+          <t>$2997173  buc  4.0
+GRILA TRANSFER CU IZOLARE FONICA, ALUMINIU MONTAT IN USA 300X200, INCLUSIV CONTRARAMA</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
@@ -6178,8 +6186,8 @@
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>$2997173  buc  4.0
-GRILA TRANSFER CU IZOLARE FONICA, ALUMINIU MONTAT IN USA 300X200, INCLUSIV CONTRARAMA</t>
+          <t>VA02B08  mp  5.0
+CANALE DREPTE CONF PE SANT CU PERIM SECT DE 400- 700 MM CU SECT CIRC DIN TABLA ZINC DE 0.5 MM</t>
         </is>
       </c>
       <c r="C279" s="8" t="inlineStr">
@@ -6199,46 +6207,46 @@
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>VA02B08  mp  5.0
-CANALE DREPTE CONF PE SANT CU PERIM SECT DE 400- 700 MM CU SECT CIRC DIN TABLA ZINC DE 0.5 MM</t>
-        </is>
-      </c>
-      <c r="C280" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D280" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="40" customHeight="1">
-      <c r="A281" s="7" t="n">
-        <v>264</v>
-      </c>
-      <c r="B281" s="8" t="inlineStr">
-        <is>
           <t>$7000777  ml  15.0
 TUBULATURA CIRCULARA RIGIDA D=100 NEIZOLATA, INCLUSIV PIESE SPECIALA SI SUPORTI</t>
         </is>
       </c>
-      <c r="C281" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D281" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="20" customHeight="1">
-      <c r="A282" s="6" t="inlineStr">
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: INSTALATII DE INCALZIRE OB.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" s="7" t="n">
+        <v>264</v>
+      </c>
+      <c r="B282" s="8" t="inlineStr">
+        <is>
+          <t>ED25A1  buc  18.0
+APARAT ELECTRIC ANTIGRIZUTOS SAU ANTIEXPLOZIV</t>
+        </is>
+      </c>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6248,8 +6256,8 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>ED25A1  buc  18.0
-APARAT ELECTRIC ANTIGRIZUTOS SAU ANTIEXPLOZIV</t>
+          <t>$2937005  buc  12.0
+RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
         </is>
       </c>
       <c r="C283" s="8" t="inlineStr">
@@ -6269,46 +6277,46 @@
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>$2937005  buc  12.0
-RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
-        </is>
-      </c>
-      <c r="C284" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D284" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="40" customHeight="1">
-      <c r="A285" s="7" t="n">
-        <v>267</v>
-      </c>
-      <c r="B285" s="8" t="inlineStr">
-        <is>
           <t>$3273416  buc  6.0
 RADIATOR ELECTRIC PE PERETE, 1000 W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL AYDESIGN STUDIO S. PROIECTANT S. C. DESIGN STUDIO SRL Atitisce LOW DERBONITA . DOMANI DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D285" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="20" customHeight="1">
-      <c r="A286" s="6" t="inlineStr">
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="20" customHeight="1">
+      <c r="A285" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: INSTALATIE VOCE-DATE-OB.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" s="7" t="n">
+        <v>267</v>
+      </c>
+      <c r="B286" s="8" t="inlineStr">
+        <is>
+          <t>TCB40A1  buc  1.0
+ASIM APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT (TELEX)</t>
+        </is>
+      </c>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6318,46 +6326,46 @@
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  1.0
-ASIM APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT (TELEX)</t>
-        </is>
-      </c>
-      <c r="C287" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D287" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="40" customHeight="1">
-      <c r="A288" s="7" t="n">
-        <v>269</v>
-      </c>
-      <c r="B288" s="8" t="inlineStr">
-        <is>
           <t>ATA01B  buc  1.0
 ASIM MONTAREA APARATELOR IN PANOURI, DULAPURI, CUTII, APARENT SAU INGROPAT CU GREUTATEA:</t>
         </is>
       </c>
-      <c r="C288" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D288" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="20" customHeight="1">
-      <c r="A289" s="6" t="inlineStr">
+      <c r="C287" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1">
+      <c r="A288" s="6" t="inlineStr">
         <is>
           <t>Categoria de lucrari: SISTEM SUPRAVEGHEREA VIDEO -OB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" s="7" t="n">
+        <v>269</v>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>TCB40B1  buc  4.0
+APARAT TELEGR. TELEIM. TRANSMIT.AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
+        </is>
+      </c>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6367,18 +6375,18 @@
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>TCB40B1  buc  4.0
-APARAT TELEGR. TELEIM. TRANSMIT.AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2700014  ml  180.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "009" - Formular F3 Formular generat cu programuf &amp;Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -6393,8 +6401,8 @@
       </c>
       <c r="C291" s="8" t="inlineStr">
         <is>
-          <t>$2700014  ml  180.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "009" - Formular F3 Formular generat cu programuf &amp;Devize (www.eDevize.ro)</t>
+          <t>EA02A1  m  180.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D291" s="9" t="inlineStr">
@@ -6403,84 +6411,70 @@
         </is>
       </c>
     </row>
-    <row r="292" ht="40" customHeight="1">
-      <c r="A292" s="7" t="n">
-        <v>272</v>
-      </c>
-      <c r="B292" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C292" s="8" t="inlineStr">
-        <is>
-          <t>EC06A1  m  180.0
-CABLU ELECTRIC DE COMANDA SEMNALIZARI BLOCARI MONTAT PE CONSOLE CU 2-30 CONDUCTE DE 0,75-2,5 MMP material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D292" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+    <row r="292" ht="20" customHeight="1">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA- (graden e 2 BUC)</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" s="7" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA01J1  mc  70.0
+TURNARE BETON SIMPLU IN STRATURI DE 5- 20CM PT.EGALIZARI LA CONSTRUCTII EDILITARE (APEDUCTE, CANALE</t>
         </is>
       </c>
       <c r="C293" s="8" t="inlineStr">
         <is>
-          <t>$3270808  m  180.0
-CABLU DATE FTP 5E 4 X 2 X AWG24 / 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" s="7" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B294" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CA02A1  mc  120.0
+TURNARE BETON ARMAT IN FUNDATII IZOLATE CỤ VOLUM &lt;3MC DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>EA02A1  m  180.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA- (graden e 2 BUC)</t>
+          <t>Categoria de lucrari: IMPREJMUIRE TEREN FOTBAL -380 ML</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" s="7" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>CA01J1  mc  70.0
-TURNARE BETON SIMPLU IN STRATURI DE 5- 20CM PT.EGALIZARI LA CONSTRUCTII EDILITARE (APEDUCTE, CANALE</t>
+          <t>TRA06A10  tona  42.5
+TRANSPORTUL RUTIER AL BETONULUI- MORTARULUI CU AUTOBETONIERA DE 5,5MC DIST. = 10KM</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
@@ -6496,29 +6490,43 @@
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>$3274584  kg  330.0
+OTEL BETON BST500 8 MM</t>
+        </is>
+      </c>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" s="7" t="n">
         <v>276</v>
       </c>
-      <c r="B297" s="8" t="inlineStr">
-        <is>
-          <t>CA02A1  mc  120.0
-TURNARE BETON ARMAT IN FUNDATII IZOLATE CỤ VOLUM &lt;3MC DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C297" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D297" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="20" customHeight="1">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: IMPREJMUIRE TEREN FOTBAL -380 ML</t>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>$2940094  kg  12850.0
+CONFECTII METALICE DIVERSE DIN PROFILE STALPI IMPREJMUIRE</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -6528,99 +6536,85 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>TRA06A10  tona  42.5
-TRANSPORTUL RUTIER AL BETONULUI- MORTARULUI CU AUTOBETONIERA DE 5,5MC DIST. = 10KM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C299" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3273618  mp  2280.0
+PLASA GARD IMPLETITA Deviz "002" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="40" customHeight="1">
-      <c r="A300" s="7" t="n">
-        <v>278</v>
-      </c>
-      <c r="B300" s="8" t="inlineStr">
-        <is>
-          <t>$3274584  kg  330.0
-OTEL BETON BST500 8 MM</t>
-        </is>
-      </c>
-      <c r="C300" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D300" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: SPATII VERZI</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" s="7" t="n">
+        <v>278</v>
+      </c>
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>TRA01A20P  tona  3373.26
+TRANSPORTUL RUTIER AL PAMINTULUI SAU MOLOZULUI CU AUTOBASCULANTA DIST .= 20 KM DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="20" customHeight="1">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: ALEI PIETONALE SI CAROSABILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" s="7" t="n">
         <v>279</v>
       </c>
-      <c r="B301" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C301" s="8" t="inlineStr">
-        <is>
-          <t>$3273618  mp  2280.0
-PLASA GARD IMPLETITA Deviz "002" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D301" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="40" customHeight="1">
-      <c r="A302" s="7" t="n">
-        <v>280</v>
-      </c>
-      <c r="B302" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C302" s="8" t="inlineStr">
-        <is>
-          <t>$2940094  kg  12850.0
-CONFECTII METALICE DIVERSE DIN PROFILE STALPI IMPREJMUIRE</t>
-        </is>
-      </c>
-      <c r="D302" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="20" customHeight="1">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: SPATII VERZI</t>
+      <c r="B303" s="8" t="inlineStr">
+        <is>
+          <t>TSC02C11  mc  5.96
+MC PAMINT UMID. NATUR DESC. AUT. TER. CAT. 1 IN COND. GOSP.APE</t>
+        </is>
+      </c>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" s="7" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B304" s="8" t="inlineStr">
         <is>
-          <t>TRA01A20P  tona  3373.26
-TRANSPORTUL RUTIER AL PAMINTULUI SAU MOLOZULUI CU AUTOBASCULANTA DIST .= 20 KM DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>TSE01D1  mp  20.0
+NIVELAREA MANUALA A TERENURILOR SI A PLATFORMELOR CU DENIVELARI DE 10-20 CM IN TEREN F. TARE</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
@@ -6636,29 +6630,43 @@
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" s="7" t="n">
+        <v>281</v>
+      </c>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>IFB09A3  mp  2000.0
+STRAT DRENANT GROSIME 5 CM DIN PIETRIS</t>
+        </is>
+      </c>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D305" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" s="7" t="n">
         <v>282</v>
       </c>
-      <c r="B305" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C305" s="8" t="inlineStr">
-        <is>
-          <t>TSH01A1  mp  59.18
-DEGAJAREA TERENULUI DE CORPURI STRAINE material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D305" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="20" customHeight="1">
-      <c r="A306" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: ALEI PIETONALE SI CAROSABILE</t>
+      <c r="B306" s="8" t="inlineStr">
+        <is>
+          <t>$2200056  mc  100.0
+PIETRIS CONCASAT -SORT 4-8 MM</t>
+        </is>
+      </c>
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D306" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6668,8 +6676,8 @@
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>TSC02C11  mc  5.96
-MC PAMINT UMID. NATUR DESC. AUT. TER. CAT. 1 IN COND. GOSP.APE</t>
+          <t>TRA01A20  tona  170.0
+TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOBASCULANTA PE DIST .= 20 KM.</t>
         </is>
       </c>
       <c r="C307" s="8" t="inlineStr">
@@ -6689,8 +6697,8 @@
       </c>
       <c r="B308" s="8" t="inlineStr">
         <is>
-          <t>TSE01D1  mp  20.0
-NIVELAREA MANUALA A TERENURILOR SI A PLATFORMELOR CU DENIVELARI DE 10-20 CM IN TEREN F. TARE</t>
+          <t>DA20A1  mp  2000.0
+MONTARE SI PROCURARE PROFIL ECOLOGOC FAGURE' ' PENTRU STABILIZARE STRAT PIETRIS</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
@@ -6710,8 +6718,8 @@
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>IFB09A3  mp  2000.0
-STRAT DRENANT GROSIME 5 CM DIN PIETRIS</t>
+          <t>DA09A01  mp  2000.0
+Strat anticontaminator din material textil netesut, filtrant(strat separator geotextil)</t>
         </is>
       </c>
       <c r="C309" s="8" t="inlineStr">
@@ -6731,8 +6739,8 @@
       </c>
       <c r="B310" s="8" t="inlineStr">
         <is>
-          <t>$2200056  mc  100.0
-PIETRIS CONCASAT -SORT 4-8 MM</t>
+          <t>$2920001  mp  0.0
+2040 000 MENBRANA GEOTEXTIL NETESUTE 150G/MP DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C310" s="8" t="inlineStr">
@@ -6746,35 +6754,21 @@
         </is>
       </c>
     </row>
-    <row r="311" ht="40" customHeight="1">
-      <c r="A311" s="7" t="n">
-        <v>287</v>
-      </c>
-      <c r="B311" s="8" t="inlineStr">
-        <is>
-          <t>TRA01A20  tona  170.0
-TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOBASCULANTA PE DIST .= 20 KM.</t>
-        </is>
-      </c>
-      <c r="C311" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D311" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="311" ht="20" customHeight="1">
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: MONTAJ BOILER OB. 4</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" s="7" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B312" s="8" t="inlineStr">
         <is>
-          <t>DA20A1  mp  2000.0
-MONTARE SI PROCURARE PROFIL ECOLOGOC FAGURE' ' PENTRU STABILIZARE STRAT PIETRIS</t>
+          <t>IA22C1  buc  7.0
+MONTARE BOILER GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Din care: Valoare aferenta utilaje termice = Valoare aferenta utilaje electrice = GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT ORIGEN STUDIE SIGN STUDIOS6 S. C. DESIGN STUDIO SRL TARGO Artisan STE- DAMBO! DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C312" s="8" t="inlineStr">
@@ -6788,35 +6782,21 @@
         </is>
       </c>
     </row>
-    <row r="313" ht="40" customHeight="1">
-      <c r="A313" s="7" t="n">
-        <v>289</v>
-      </c>
-      <c r="B313" s="8" t="inlineStr">
-        <is>
-          <t>DA09A01  mp  2000.0
-Strat anticontaminator din material textil netesut, filtrant(strat separator geotextil)</t>
-        </is>
-      </c>
-      <c r="C313" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D313" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="313" ht="20" customHeight="1">
+      <c r="A313" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII VENTILATIE OB. 4</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" s="7" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B314" s="8" t="inlineStr">
         <is>
-          <t>$2920001  mp  0.0
-2040 000 MENBRANA GEOTEXTIL NETESUTE 150G/MP DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>VC01C1  buc  4.0
+MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
         </is>
       </c>
       <c r="C314" s="8" t="inlineStr">
@@ -6830,38 +6810,66 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="20" customHeight="1">
-      <c r="A315" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: MONTAJ BOILER OB. 4</t>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" s="7" t="n">
+        <v>289</v>
+      </c>
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>$3270546  buc  3.0
+VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
+        </is>
+      </c>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D315" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" s="7" t="n">
+        <v>290</v>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
+          <t>$3272502  buc  1.0
+VENTILATOR BAIE SILENT-100CZ - D=100 - 230V - 95 M3/H - SOLER PALAU</t>
+        </is>
+      </c>
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D316" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" s="7" t="n">
         <v>291</v>
       </c>
-      <c r="B316" s="8" t="inlineStr">
-        <is>
-          <t>IA22C1  buc  7.0
-MONTARE BOILER GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Din care: Valoare aferenta utilaje termice = Valoare aferenta utilaje electrice = GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT ORIGEN STUDIE SIGN STUDIOS6 S. C. DESIGN STUDIO SRL TARGO Artisan STE- DAMBO! DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C316" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D316" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="20" customHeight="1">
-      <c r="A317" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII VENTILATIE OB. 4</t>
+      <c r="B317" s="8" t="inlineStr">
+        <is>
+          <t>VB14D1  buc  2.0
+PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
+        </is>
+      </c>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -6871,8 +6879,8 @@
       </c>
       <c r="B318" s="8" t="inlineStr">
         <is>
-          <t>VC01C1  buc  4.0
-MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
+          <t>$7002221  buc  1.0
+GRILA VENTILATIE DN110 MM</t>
         </is>
       </c>
       <c r="C318" s="8" t="inlineStr">
@@ -6892,8 +6900,8 @@
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>$3270546  buc  3.0
-VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
+          <t>$2997228  buc  2.0
+GRILA EXTERIOARE CU JALUZELE FIXE, Dn125, cu jaluzele anti-ploaie si plasa antiinsecte</t>
         </is>
       </c>
       <c r="C319" s="8" t="inlineStr">
@@ -6913,8 +6921,8 @@
       </c>
       <c r="B320" s="8" t="inlineStr">
         <is>
-          <t>$3272502  buc  1.0
-VENTILATOR BAIE SILENT-100CZ - D=100 - 230V - 95 M3/H - SOLER PALAU</t>
+          <t>VB30A1  buc  4.0
+ANEMOSTAT PLAN PATRAT DET TIP 61/272 DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C320" s="8" t="inlineStr">
@@ -6928,35 +6936,21 @@
         </is>
       </c>
     </row>
-    <row r="321" ht="40" customHeight="1">
-      <c r="A321" s="7" t="n">
-        <v>295</v>
-      </c>
-      <c r="B321" s="8" t="inlineStr">
-        <is>
-          <t>VB14D1  buc  2.0
-PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
-        </is>
-      </c>
-      <c r="C321" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D321" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="321" ht="20" customHeight="1">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII INCALZIRE OB. 4</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" s="7" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B322" s="8" t="inlineStr">
         <is>
-          <t>$7002221  buc  1.0
-GRILA VENTILATIE DN110 MM</t>
+          <t>ED25A1  buc  27.0
+APARAT ELECTRIC ANTIGRIZUTOS SAU</t>
         </is>
       </c>
       <c r="C322" s="8" t="inlineStr">
@@ -6972,12 +6966,12 @@
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" s="7" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>$2997228  buc  2.0
-GRILA EXTERIOARE CU JALUZELE FIXE, Dn125, cu jaluzele anti-ploaie si plasa antiinsecte</t>
+          <t>$2937005  buc  12.0
+RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
         </is>
       </c>
       <c r="C323" s="8" t="inlineStr">
@@ -6993,61 +6987,61 @@
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" s="7" t="n">
+        <v>297</v>
+      </c>
+      <c r="B324" s="8" t="inlineStr">
+        <is>
+          <t>$3273416  buc  6.0
+RADIATOR ELECTRIC PE PERETE, 1000 W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE</t>
+        </is>
+      </c>
+      <c r="C324" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="B324" s="8" t="inlineStr">
-        <is>
-          <t>VB30A1  buc  4.0
-ANEMOSTAT PLAN PATRAT DET TIP 61/272 DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C324" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D324" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="20" customHeight="1">
-      <c r="A325" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII INCALZIRE OB. 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="40" customHeight="1">
-      <c r="A326" s="7" t="n">
-        <v>299</v>
-      </c>
-      <c r="B326" s="8" t="inlineStr">
-        <is>
-          <t>ED25A1  buc  27.0
-APARAT ELECTRIC ANTIGRIZUTOS SAU</t>
-        </is>
-      </c>
-      <c r="C326" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D326" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+      <c r="B325" s="8" t="inlineStr">
+        <is>
+          <t>$5700801  buc  9.0
+RADIATOR ELECTRIC MONTAJ PE PERETE 1500W, PREVAZUT CU TERMOASTAL REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT S. C. DESIGN STUDIO SRL GOVISTE . DAMBOVITA - ROM DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="20" customHeight="1">
+      <c r="A326" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INST. CLIMATIZARE OB. 4</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" s="7" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>$2937005  buc  12.0
-RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
+          <t>VC1011  buc  3.0
+MONTAT APARAT AER CONDITIONAT</t>
         </is>
       </c>
       <c r="C327" s="8" t="inlineStr">
@@ -7063,12 +7057,12 @@
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" s="7" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B328" s="8" t="inlineStr">
         <is>
-          <t>$3273416  buc  6.0
-RADIATOR ELECTRIC PE PERETE, 1000 W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE</t>
+          <t>$2000005  buc  1.0
+SUPORT APARAT AER CONDITIONAT</t>
         </is>
       </c>
       <c r="C328" s="8" t="inlineStr">
@@ -7084,29 +7078,43 @@
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" s="7" t="n">
+        <v>301</v>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t>IC31A1#  m  36.0
+TEAVA DIN CUPRU MONTATA PRIN SUDURA LA LEGATURA CORPURILOR AI APARATELOR DE INSTALATIILE DE IMCALZIRE CENTRALA CU DIAMETRUL EXTERIOR DE PANA LA 15.0 MM INCLUSIV</t>
+        </is>
+      </c>
+      <c r="C329" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" s="7" t="n">
         <v>302</v>
       </c>
-      <c r="B329" s="8" t="inlineStr">
-        <is>
-          <t>$5700801  buc  9.0
-RADIATOR ELECTRIC MONTAJ PE PERETE 1500W, PREVAZUT CU TERMOASTAL REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT S. C. DESIGN STUDIO SRL GOVISTE . DAMBOVITA - ROM DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C329" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D329" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="330" ht="20" customHeight="1">
-      <c r="A330" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INST. CLIMATIZARE OB. 4</t>
+      <c r="B330" s="8" t="inlineStr">
+        <is>
+          <t>$3272370  m  18.0
+TEAVA DIN CUPRU COLAC 1/4 (6,35 MM) PENTRU AER CONDITIONAT</t>
+        </is>
+      </c>
+      <c r="C330" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
@@ -7116,8 +7124,8 @@
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>VC1011  buc  3.0
-MONTAT APARAT AER CONDITIONAT</t>
+          <t>$3272371  m  18.0
+TEAVA CUPRU COLAC 50 M IZOLATA 3/8 (9.52 MM) PENTRU AER CONDITIONAT</t>
         </is>
       </c>
       <c r="C331" s="8" t="inlineStr">
@@ -7137,8 +7145,8 @@
       </c>
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t>$2000005  buc  1.0
-SUPORT APARAT AER CONDITIONAT</t>
+          <t>FI14A1  tona  3.0
+VACUUMAREA SI UMPLEREA INSTAL CU AGENT FRIGORIFIC : AMONIAC</t>
         </is>
       </c>
       <c r="C332" s="8" t="inlineStr">
@@ -7158,8 +7166,8 @@
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>IC31A1#  m  36.0
-TEAVA DIN CUPRU MONTATA PRIN SUDURA LA LEGATURA CORPURILOR AI APARATELOR DE INSTALATIILE DE IMCALZIRE CENTRALA CU DIAMETRUL EXTERIOR DE PANA LA 15.0 MM INCLUSIV</t>
+          <t>$7322835  kg  3.0
+FREON DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C333" s="8" t="inlineStr">
@@ -7173,35 +7181,21 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="40" customHeight="1">
-      <c r="A334" s="7" t="n">
-        <v>306</v>
-      </c>
-      <c r="B334" s="8" t="inlineStr">
-        <is>
-          <t>$3272370  m  18.0
-TEAVA DIN CUPRU COLAC 1/4 (6,35 MM) PENTRU AER CONDITIONAT</t>
-        </is>
-      </c>
-      <c r="C334" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D334" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="334" ht="20" customHeight="1">
+      <c r="A334" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATIE VOCE-DATE-OB. 4</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" s="7" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>$3272371  m  18.0
-TEAVA CUPRU COLAC 50 M IZOLATA 3/8 (9.52 MM) PENTRU AER CONDITIONAT</t>
+          <t>TCB40A1  buc  1.0
+APARAT TELEGR. TELEIM. TRANSMIT.AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
         </is>
       </c>
       <c r="C335" s="8" t="inlineStr">
@@ -7217,12 +7211,12 @@
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" s="7" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B336" s="8" t="inlineStr">
         <is>
-          <t>FI14A1  tona  3.0
-VACUUMAREA SI UMPLEREA INSTAL CU AGENT FRIGORIFIC : AMONIAC</t>
+          <t>ATA01B  buc  1.0
+MONTAREA APARATELOR IN PANOURI, DULAPURI, CUTII, APARENT SAU INGROPAT CU GREUTATEA:</t>
         </is>
       </c>
       <c r="C336" s="8" t="inlineStr">
@@ -7238,29 +7232,43 @@
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" s="7" t="n">
+        <v>308</v>
+      </c>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>$7701266  buc  1.0
+UPS RACKTABIL 1.5 KVA</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" s="7" t="n">
         <v>309</v>
       </c>
-      <c r="B337" s="8" t="inlineStr">
-        <is>
-          <t>$7322835  kg  3.0
-FREON DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C337" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D337" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="20" customHeight="1">
-      <c r="A338" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATIE VOCE-DATE-OB. 4</t>
+      <c r="B338" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C338" s="8" t="inlineStr">
+        <is>
+          <t>$6718506  ml  1900.0
+BANDA AVERTIZOARE PVC INSCRIPTIONATA PENTRU CABLU TELECOMUNICATII IN SAPATURA 1 MM GROSIME Deviz "004" - Formular F3 Formular generat cu programul eDevize (www.eDevize.ro)</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
@@ -7270,87 +7278,73 @@
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  1.0
-APARAT TELEGR. TELEIM. TRANSMIT.AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C339" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DF26A12]  m  1900.0
+Banda de semnalizare material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="40" customHeight="1">
-      <c r="A340" s="7" t="n">
-        <v>311</v>
-      </c>
-      <c r="B340" s="8" t="inlineStr">
-        <is>
-          <t>ATA01B  buc  1.0
-MONTAREA APARATELOR IN PANOURI, DULAPURI, CUTII, APARENT SAU INGROPAT CU GREUTATEA:</t>
-        </is>
-      </c>
-      <c r="C340" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D340" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="20" customHeight="1">
+      <c r="A340" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: SISTEM SUPRAVEGHEREA VIDEO -OB4</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" s="7" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TCB40A1  buc  2.0
+APARAT TELEGR. TELEIM. TRANSMIT . AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT (TELEX)</t>
         </is>
       </c>
       <c r="C341" s="8" t="inlineStr">
         <is>
-          <t>$5538123  buc  1.0
-PATCHPANEL 8 PORTURI RJ45 ECHIPAT Deviz "009" - Formular F3 Formular generat cu programul Devize (www.eDevize.ro)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D341" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" s="7" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B342" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TCB40B1  buc  4.0
+APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
         </is>
       </c>
       <c r="C342" s="8" t="inlineStr">
         <is>
-          <t>$2600000  buc  1.0
-SWITCH 8 PORTURI RJ45</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" s="7" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
@@ -7359,8 +7353,8 @@
       </c>
       <c r="C343" s="8" t="inlineStr">
         <is>
-          <t>$7701266  buc  1.0
-UPS RACKTABIL 1.5 KVA</t>
+          <t>$2700014  ml  200.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "010" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D343" s="9" t="inlineStr">
@@ -7371,7 +7365,7 @@
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" s="7" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B344" s="8" t="inlineStr">
         <is>
@@ -7380,8 +7374,8 @@
       </c>
       <c r="C344" s="8" t="inlineStr">
         <is>
-          <t>$5538123  buc  1.0
-PATCHPANEL 8 PORTURI RJ45 ECHIPAT Deviz "008" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
+          <t>EA02A1  m  200.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D344" s="9" t="inlineStr">
@@ -7390,84 +7384,84 @@
         </is>
       </c>
     </row>
-    <row r="345" ht="40" customHeight="1">
-      <c r="A345" s="7" t="n">
-        <v>316</v>
-      </c>
-      <c r="B345" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C345" s="8" t="inlineStr">
-        <is>
-          <t>$2600000  buc  1.0
-SWITCH 8 PORTURI RJ45</t>
-        </is>
-      </c>
-      <c r="D345" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+    <row r="345" ht="20" customHeight="1">
+      <c r="A345" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII VENTILATIE OB.5</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" s="7" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VC01C1  buc  2.0
+MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
         </is>
       </c>
       <c r="C346" s="8" t="inlineStr">
         <is>
-          <t>DF26A12]  m  1900.0
-Banda de semnalizare material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" s="7" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3270546  buc  2.0
+VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
         </is>
       </c>
       <c r="C347" s="8" t="inlineStr">
         <is>
-          <t>$6718506  ml  1900.0
-BANDA AVERTIZOARE PVC INSCRIPTIONATA PENTRU CABLU TELECOMUNICATII IN SAPATURA 1 MM GROSIME Deviz "004" - Formular F3 Formular generat cu programul eDevize (www.eDevize.ro)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="20" customHeight="1">
-      <c r="A348" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: SISTEM SUPRAVEGHEREA VIDEO -OB4</t>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" s="7" t="n">
+        <v>317</v>
+      </c>
+      <c r="B348" s="8" t="inlineStr">
+        <is>
+          <t>VB14D1  buc  2.0
+PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
+        </is>
+      </c>
+      <c r="C348" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" s="7" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  2.0
-APARAT TELEGR. TELEIM. TRANSMIT . AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT (TELEX)</t>
+          <t>$7002221  buc  2.0
+GRILA VENTILATIE DN110 MM</t>
         </is>
       </c>
       <c r="C349" s="8" t="inlineStr">
@@ -7483,12 +7477,12 @@
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" s="7" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B350" s="8" t="inlineStr">
         <is>
-          <t>TCB40B1  buc  4.0
-APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
+          <t>VB30A1  buc  2.0
+ANEMOSTAT PLAN PATRAT DET TIP 61/272</t>
         </is>
       </c>
       <c r="C350" s="8" t="inlineStr">
@@ -7504,103 +7498,103 @@
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" s="7" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2997173  buc  2.0
+GRILA TRANSFER CU IZOLARE FONICA, ALUMINIU MONTAT IN USA 300X200, INCLUSIV CONTRARAMA</t>
         </is>
       </c>
       <c r="C351" s="8" t="inlineStr">
         <is>
-          <t>$3270808  m  200.0
-CABLU DATE FTP 5E 4 X 2 X AWG24 / 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" s="7" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B352" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VA02B08  mp  2.0
+CANALE DREPTE CONF PE SANT CU PERIM SECT DE 400- 700 MM CU SECT CIRC DIN TABLA ZINC DE 0.5 MM</t>
         </is>
       </c>
       <c r="C352" s="8" t="inlineStr">
         <is>
-          <t>EA02A1  m  200.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" s="7" t="n">
+        <v>322</v>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
+          <t>$7000777  ml  6.0
+TUBULATURA CIRCULARA RIGIDA D=100 NEIZOLATA, INCLUSIV PIESE SPECIALA SI SUPORTI DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C353" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="20" customHeight="1">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII TERMICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" s="7" t="n">
         <v>323</v>
       </c>
-      <c r="B353" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C353" s="8" t="inlineStr">
-        <is>
-          <t>$2700014  ml  200.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "010" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D353" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="40" customHeight="1">
-      <c r="A354" s="7" t="n">
-        <v>324</v>
-      </c>
-      <c r="B354" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C354" s="8" t="inlineStr">
-        <is>
-          <t>EC06A1  m  200.0
-CABLU ELECTRIC DE COMANDA SEMNALIZARI BLOCARI MONTAT PE CONSOLE CU 2-30 CONDUCTE DE 0,75-2,5 MMP material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D354" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="20" customHeight="1">
-      <c r="A355" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII VENTILATIE OB.5</t>
+      <c r="B355" s="8" t="inlineStr">
+        <is>
+          <t>ED25A1  buc  4.0
+APARAT ELECTRIC ANTIGRIZUTOS SAU</t>
+        </is>
+      </c>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" s="7" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B356" s="8" t="inlineStr">
         <is>
-          <t>VC01C1  buc  2.0
-MONTAREA VENTILATORULUI AXIAL GR. TOTALA 50-200KG</t>
+          <t>$2937005  buc  2.0
+RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
         </is>
       </c>
       <c r="C356" s="8" t="inlineStr">
@@ -7616,12 +7610,12 @@
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" s="7" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>$3270546  buc  2.0
-VENTILATOR BAIE D=100MM, MODEL : "EOL 100T" TIMER</t>
+          <t>$3273416  buc  2.0
+RADIATOR ELECTRIC PE PERETE, 1000 W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL * D. VGIL STUDIO S. PROIECTANT S.C. DESIGN STUDIO SRL Datisa DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
         </is>
       </c>
       <c r="C357" s="8" t="inlineStr">
@@ -7635,35 +7629,21 @@
         </is>
       </c>
     </row>
-    <row r="358" ht="40" customHeight="1">
-      <c r="A358" s="7" t="n">
-        <v>327</v>
-      </c>
-      <c r="B358" s="8" t="inlineStr">
-        <is>
-          <t>VB14D1  buc  2.0
-PRIZA DE AER DET TIP 61/105 AVIND PERIMETRUL 1401-2500 MM MONTATA PE CANAL</t>
-        </is>
-      </c>
-      <c r="C358" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D358" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="358" ht="20" customHeight="1">
+      <c r="A358" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: SISTEM SUPRAVEGHEREA VIDEO -OB5</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" s="7" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>$7002221  buc  2.0
-GRILA VENTILATIE DN110 MM</t>
+          <t>TCB40A1  buc  1.0
+APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
         </is>
       </c>
       <c r="C359" s="8" t="inlineStr">
@@ -7679,12 +7659,12 @@
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" s="7" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B360" s="8" t="inlineStr">
         <is>
-          <t>VB30A1  buc  2.0
-ANEMOSTAT PLAN PATRAT DET TIP 61/272</t>
+          <t>TCB40B1  buc  2.0
+APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
         </is>
       </c>
       <c r="C360" s="8" t="inlineStr">
@@ -7700,103 +7680,89 @@
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" s="7" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>$2997173  buc  2.0
-GRILA TRANSFER CU IZOLARE FONICA, ALUMINIU MONTAT IN USA 300X200, INCLUSIV CONTRARAMA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C361" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2700014  ml  100.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "007" - Formular F3 Formular generat cu programul Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" s="7" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t>VA02B08  mp  2.0
-CANALE DREPTE CONF PE SANT CU PERIM SECT DE 400- 700 MM CU SECT CIRC DIN TABLA ZINC DE 0.5 MM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C362" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EA02A1  m  100.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="363" ht="40" customHeight="1">
-      <c r="A363" s="7" t="n">
-        <v>332</v>
-      </c>
-      <c r="B363" s="8" t="inlineStr">
-        <is>
-          <t>$7000777  ml  6.0
-TUBULATURA CIRCULARA RIGIDA D=100 NEIZOLATA, INCLUSIV PIESE SPECIALA SI SUPORTI DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
-        </is>
-      </c>
-      <c r="C363" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D363" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="364" ht="20" customHeight="1">
-      <c r="A364" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII TERMICE</t>
-        </is>
-      </c>
-    </row>
-    <row r="365" ht="40" customHeight="1">
-      <c r="A365" s="7" t="n">
-        <v>333</v>
-      </c>
-      <c r="B365" s="8" t="inlineStr">
-        <is>
-          <t>ED25A1  buc  4.0
-APARAT ELECTRIC ANTIGRIZUTOS SAU</t>
-        </is>
-      </c>
-      <c r="C365" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D365" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="20" customHeight="1">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATIE VOCE-DATE-OB.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="40" customHeight="1">
+      <c r="A364" s="7" t="n">
+        <v>330</v>
+      </c>
+      <c r="B364" s="8" t="inlineStr">
+        <is>
+          <t>TCB40A1  buc  1.0
+APARAT TELEGR. TELEIM. TRANSMIT . AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
+        </is>
+      </c>
+      <c r="C364" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D364" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="20" customHeight="1">
+      <c r="A365" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATIE IRIGATIE SPATII VERZI</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" s="7" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B366" s="8" t="inlineStr">
         <is>
-          <t>$2937005  buc  2.0
-RADIATOR ELECTRIC PE PERETE, 500W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTII</t>
+          <t>DF26A1  m  3350.0
+Banda de semnalizare</t>
         </is>
       </c>
       <c r="C366" s="8" t="inlineStr">
@@ -7812,12 +7778,12 @@
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" s="7" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>$3273416  buc  2.0
-RADIATOR ELECTRIC PE PERETE, 1000 W, PREVAZUT CU TERMOASTAT REGLABIL, INCLUSIV SUPORTI SI ACCESORII DE PRINDERE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL * D. VGIL STUDIO S. PROIECTANT S.C. DESIGN STUDIO SRL Datisa DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>$7000763  ml  3350.0
+BANDA DE INSERTIE METALICA DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev / 2024</t>
         </is>
       </c>
       <c r="C367" s="8" t="inlineStr">
@@ -7834,18 +7800,18 @@
     <row r="368" ht="20" customHeight="1">
       <c r="A368" s="6" t="inlineStr">
         <is>
-          <t>Categoria de lucrari: SISTEM SUPRAVEGHEREA VIDEO -OB5</t>
+          <t>Categoria de lucrari: ORG. SANTIER- CONTAINER</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" s="7" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  1.0
-APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
+          <t>CL08B1  buc  2.0
+MONTARE BARACA</t>
         </is>
       </c>
       <c r="C369" s="8" t="inlineStr">
@@ -7861,12 +7827,12 @@
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" s="7" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B370" s="8" t="inlineStr">
         <is>
-          <t>TCB40B1  buc  2.0
-APARAT TELEGR. TELEIM. TRANSMIT. AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: OFICIU</t>
+          <t>$7000367  buc  2.0
+BARACA TIP CONTAINER, IZOLAT TERMIC</t>
         </is>
       </c>
       <c r="C370" s="8" t="inlineStr">
@@ -7882,82 +7848,82 @@
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" s="7" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TRA02A50  tona  4.0
+TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOCAMIONUL PE DIST .= 50 KM.</t>
         </is>
       </c>
       <c r="C371" s="8" t="inlineStr">
         <is>
-          <t>$3270808  m  100.0
-CABLU DATE FTP 5E 4 X 2 X AWG24 / 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" s="7" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B372" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AUT6752  ora  20.0
+AUTOMACARA 6- 9,9TF CU BRAT CU ZABRELE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Din care: Valoare aferenta utilaje termice = Valoare aferenta utilaje electrice = Detaliere transporturi: -Articole TRA GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024 y PROIECTANT S. C. DESIGN STUDIO SRL DAMBOVITA-</t>
         </is>
       </c>
       <c r="C372" s="8" t="inlineStr">
         <is>
-          <t>EA02A1  m  100.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="373" ht="40" customHeight="1">
-      <c r="A373" s="7" t="n">
-        <v>340</v>
-      </c>
-      <c r="B373" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C373" s="8" t="inlineStr">
-        <is>
-          <t>$2700014  ml  100.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "007" - Formular F3 Formular generat cu programul Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D373" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="374" ht="20" customHeight="1">
-      <c r="A374" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATIE VOCE-DATE-OB.5</t>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="20" customHeight="1">
+      <c r="A373" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: ORG SANTIER- MONTARE WC ECOLOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" s="7" t="n">
+        <v>337</v>
+      </c>
+      <c r="B374" s="8" t="inlineStr">
+        <is>
+          <t>CL20C1  kg  500.0
+MONTAREA CONFECTIILOR METALICE APARENTE: DIVERSE EXCLUSIV PARAPETI, BALUSTRAZI, CHEPENGURI</t>
+        </is>
+      </c>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D374" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" s="7" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>TCB40A1  buc  1.0
-APARAT TELEGR. TELEIM. TRANSMIT . AUTOM. RECEPTOR PERFORATOR (MANUAL) PT: ABONAT</t>
+          <t>$4104443  zi  730.0
+COSTUL INCHIRIERI WC ECOLOGIC</t>
         </is>
       </c>
       <c r="C375" s="8" t="inlineStr">
@@ -7971,226 +7937,240 @@
         </is>
       </c>
     </row>
-    <row r="376" ht="20" customHeight="1">
-      <c r="A376" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATIE IRIGATIE SPATII VERZI</t>
-        </is>
-      </c>
-    </row>
-    <row r="377" ht="40" customHeight="1">
-      <c r="A377" s="7" t="n">
-        <v>342</v>
-      </c>
-      <c r="B377" s="8" t="inlineStr">
-        <is>
-          <t>DF26A1  m  3350.0
-Banda de semnalizare</t>
-        </is>
-      </c>
-      <c r="C377" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D377" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+    <row r="376" ht="40" customHeight="1">
+      <c r="A376" s="7" t="n">
+        <v>339</v>
+      </c>
+      <c r="B376" s="8" t="inlineStr">
+        <is>
+          <t>TRA02A50  tona  1.0
+TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOCAMIONUL PE DIST .= 50 KM. GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Detaliere transporturi: -Articole TRA GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT S. C. DESIGN STUDIO SRL · DAMBOV Attesa DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+        </is>
+      </c>
+      <c r="C376" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D376" s="9" t="inlineStr">
+        <is>
+          <t>LIPSĂ ARTICOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="20" customHeight="1">
+      <c r="A377" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: INSTALATII ELECTRICE curenti tari OB.5</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" s="7" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B378" s="8" t="inlineStr">
         <is>
-          <t>$7000763  ml  3350.0
-BANDA DE INSERTIE METALICA DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev / 2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C378" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2700014  ml  95.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "006" - Formular F3 Formular generat cu programul eDevize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D378" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="379" ht="20" customHeight="1">
-      <c r="A379" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: ORG. SANTIER- CONTAINER</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="40" customHeight="1">
+      <c r="A379" s="7" t="n">
+        <v>341</v>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>EA02A1  m  225.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D379" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" s="7" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B380" s="8" t="inlineStr">
         <is>
-          <t>CL08B1  buc  2.0
-MONTARE BARACA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C380" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EA02A1  m  95.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" s="7" t="n">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>$7000367  buc  2.0
-BARACA TIP CONTAINER, IZOLAT TERMIC</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C381" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2700014  ml  1486.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "008" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" s="7" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B382" s="8" t="inlineStr">
         <is>
-          <t>TRA02A50  tona  4.0
-TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOCAMIONUL PE DIST .= 50 KM.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C382" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EA02A1  m  1450.0
+TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" s="7" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>AUT6752  ora  20.0
-AUTOMACARA 6- 9,9TF CU BRAT CU ZABRELE GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Din care: Valoare aferenta utilaje termice = Valoare aferenta utilaje electrice = Detaliere transporturi: -Articole TRA GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024 y PROIECTANT S. C. DESIGN STUDIO SRL DAMBOVITA-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C383" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$2700014  ml  225.0
+TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "007" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="384" ht="20" customHeight="1">
       <c r="A384" s="6" t="inlineStr">
         <is>
-          <t>Categoria de lucrari: ORG SANTIER- MONTARE WC ECOLOGIC</t>
+          <t>Categoria de lucrari: ALIMENTARE CU APA e Devize Formular F3 Lista cu cantitati de lucrari pe categorii de lucrari SECTIUNEA TEHNICA SECTIUNEA FINANCIARA Nr. Capitol de lucrari U.M. Cantitatea Pretul unitar (fara TVA) - Lei - TOTALUL (fara TVA) - Lei - 0 1 2 3 4 5 = 3 x 4 1 ACA10A2 - MONTARE TEAVA PVC TIP 4 (G) IN PAMINT IN EXTERIORULCLADIRILOR, AVIND DN 32 M 30.000 6.63 199.02 material: 0.00 0.00 manopera: 6.60 197.88 utilaj: 0.04 1.14 transport: 0.00 0.00 1 3276650 - TEAVA PEHD 80 PENTRU TRANSPORT APA POTABILA, SDR 17, DN 32, PN 10 BAR M 31.500 5.00 157.50 2 ACA11A3 - MONTARE TEAVA PVC TIP 3 (M) IN PAMINT, I IN EXTERIORULCLADIRILOR, AVIND DN 40 M 210.000 6.37 1,337.73 material: 0.00 0.00 manopera: 6.33 1,329.75 utilaj: 0.04 7.97 transport: 0.00 0.00 2 3276850 - TEAVA PEHD 80 PENTRU TRANSPORT APA POTABILA, SDR 17, DN 40, PN 10 BAR M 220.500 7.00 1,543.50 3 ACA10B1 - MONTARE TEAVA PVC TIP 4 (G) IN PAMINT IN EXTERIORULCLADIRILOR, AVIND DN 50 M 5.000 6.63 33.17 material: 0.00 0.00 manopera: 6.60 32.98 utilaj: 0.04 0.19 transport: 0.00 0.00 3 3276846 - TEAVA PEHD 80 PENTRU TRANSPORT APA POTABILA, SDR 17, DN 50, PN 10 BAR M 5.000 10.00 50.00 4 ACA10B2 - MONTARE TEAVA PVC TIP 4 (G) IN PAMINT IN EXTERIORULCLADIRILOR, AVIND DN 63 M 100.000 6.63 663.40 material: 0.00 0.00 manopera: 6.60 659.60 utilaj: 0.04 3.80 transport: 0.00 0.00 4 3276844 - TEAVA PEHD 80 PENTRU TRANSPORT APA POTABILA, SDR 17, DN 63, PN 10 BAR M 105.000 17.00 1,785.00 5 ACD04A1 - CAMIN VIZITARE STAS 2448-73 CU CAMERA LUCRU HC = 2M DIN TUB BET. CU CEP SI BUZA LA CANALE CU DN 200 BUC. 1.000 386.46 386.46 material: 0.00 0.00 manopera: 287.46 287.46 utilaj: 99.00 99.00 transport: 0.00 0.00 5 3274594 - CAMIN DUBLUSTRAT PT. APOMETRU CU INSTALATIE 3/4 ' ' SI CAPAC D.550 H.1100MM BUC. 1.000 1,400.00 1,400.00 Deviz "001" - Formular F3 17,7 Formular generat cu programul @Devize (www.eDevize.ro) Pagina 1 din 4</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" s="7" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>CL20C1  kg  500.0
-MONTAREA CONFECTIILOR METALICE APARENTE: DIVERSE EXCLUSIV PARAPETI, BALUSTRAZI, CHEPENGURI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C385" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$3274594  buc  1.0
+CAMIN DUBLUSTRAT PT. APOMETRU CU INSTALATIE 3/4 ' ' SI CAPAC D.550 H.1100MM Deviz "001" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro) Pagina 1 din 4</t>
         </is>
       </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="386" ht="40" customHeight="1">
-      <c r="A386" s="7" t="n">
-        <v>349</v>
-      </c>
-      <c r="B386" s="8" t="inlineStr">
-        <is>
-          <t>$4104443  zi  730.0
-COSTUL INCHIRIERI WC ECOLOGIC</t>
-        </is>
-      </c>
-      <c r="C386" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D386" s="9" t="inlineStr">
-        <is>
-          <t>LIPSĂ ARTICOL</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="20" customHeight="1">
+      <c r="A386" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: ALIMENTARE CU E.E. SI ILUMINAT EXTERIOR e Devize Formular F3 Lista cu cantitati de lucrari pe categorii de lucrari SECTIUNEA TEHNICA SECTIUNEA FINANCIARA Nr. Capitol de lucrari U.M. Cantitatea Pretul unitar (fara TVA) - Lei - TOTALUL (fara TVA) - Lei - 0 1 2 3 4 5 = 3 x 4 1 TSA16C1 - SAP.MAN. IN TRANSEE PT.CABL.EL.IN PAM.CU UMID. NAT. FARA SPRIJ. LAT. &lt; 1M, ADINC. &lt; 1,5M, T. TARE M.C. 340.000 58.57 19,914.64 material: 0.00 0.00 manopera: 58.57 19,914.64 utilaj: 0.00 0.00 transport: 0.00 0.00 2 W2H04A1 - STRAT NISIP ASEZAT IN SANT PENTRU PROTEJAREA CABLURILOR LA LUCR IN PROF NETIPIZAT M.C. 68.000 138.03 9,386.03 material: 126.00 8,567.92 manopera: 12.03 818.12 utilaj: 0.00 0.00 transport: 0.00 0.00 3 TRA01A20 - TRANSPORTUL RUTIER AL MATERIALELOR, SEMI FABRICATELOR CU AUTOBASCULANTA PE DIST. 20 KM. TONA 122.400 28.00 3,427.20 material: 0.00 0.00 manopera: 0.00 0.00 utilaj: 0.00 0.00 transport: 28.00 3,427.20 4 W1S59A - IDENTIFICAREA CABLURILOR IN PROFILE M 850.000 1.58 1,345.58 material: 0.00 0.00 manopera: 1.58 1,345.58 utilaj: 0.00 0.00 transport: 0.00 0.00 4 2946062 - FOLIE PVC INSCRIPTIONAT, PENTRU AVERTIZARE CABLU SUB TENSIUNE ML. 850.000 3.00 2,550.00 5 W2G02B31 - MONT. CABLU SUBT.1 KV GR 2,901-3,200 KG / M CU - AL IN TUB PE TRASEU CU OBST. TR. MANUALA MONT M 100.000 7.36 736.23 material: 0.64 63.81 manopera: 6.72 672.42 utilaj: 0.00 0.00 transport: 0.00 0.00 5 3275680 - CABLURI ELECTRICE CYABY - F 3X95 + 50, 71760471360100, ICME ECAB M 100.000 185.00 18,500.00 6 ACA11D1 - MONTARE TEAVA PVC TIP 3 (M) IN PAMINT, IN EXTERIORULCLADIRILOR, AVIND DN 110 M 100.000 8.74 874.47 material: 0.00 0.00 manopera: 8.71 870.67 utilaj: 0.04 3.80 transport: 0.00 0.00 6 3272541 - TUB PROTECTIE CABLU D.110 GOFRAT ALBASTRU DUBLU STRAT 450N L6M M 100.000 11.00 1,100.00 Deviz "003" - Formular F3 185 Formular generat cu programul @Devize (www.eDevize.ro) Pagina 1 din 5</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" s="7" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>TRA02A50  tona  1.0
-TRANSPORTUL RUTIER AL MATERIALELOR, SEMIFABRICATELOR CU AUTOCAMIONUL PE DIST .= 50 KM. GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL Detaliere transporturi: -Articole TRA GREUTATE MATERIALE MANOPERA UTILAJ TRANSPORT TOTAL PROIECTANT S. C. DESIGN STUDIO SRL · DAMBOV Attesa DESIGN STUDIO S.R.L. - proiect inițial 424/2018 - proiect actualizat integral 424-rev/ 2024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C387" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>W2G02B31  m  100.0
+MONT. CABLU SUBT.1 KV GR 2,901-3,200 KG / M CU - AL IN TUB PE TRASEU CU OBST. TR. MANUALA MONT material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D387" s="9" t="inlineStr">
         <is>
-          <t>LIPSĂ ARTICOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="388" ht="20" customHeight="1">
-      <c r="A388" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: ARHITECTURA teren tenis si grupuri sanitare</t>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="40" customHeight="1">
+      <c r="A388" s="7" t="n">
+        <v>348</v>
+      </c>
+      <c r="B388" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C388" s="8" t="inlineStr">
+        <is>
+          <t>W2H04A1  mc  68.0
+STRAT NISIP ASEZAT IN SANT PENTRU PROTEJAREA CABLURILOR LA LUCR IN PROF NETIPIZAT material: manopera: utilaj: transport:</t>
+        </is>
+      </c>
+      <c r="D388" s="9" t="inlineStr">
+        <is>
+          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" s="7" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
@@ -8199,8 +8179,8 @@
       </c>
       <c r="C389" s="8" t="inlineStr">
         <is>
-          <t>$3276725  kg  2040.0
-TINCI PT TENCUIELI FINE</t>
+          <t>$3272541  m  100.0
+TUB PROTECTIE CABLU D.110 GOFRAT ALBASTRU DUBLU STRAT 450N L6M Deviz "003" - Formular F3</t>
         </is>
       </c>
       <c r="D389" s="9" t="inlineStr">
@@ -8209,30 +8189,16 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="40" customHeight="1">
-      <c r="A390" s="7" t="n">
-        <v>352</v>
-      </c>
-      <c r="B390" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C390" s="8" t="inlineStr">
-        <is>
-          <t>$2401678  mp  223.65
-FAIANTA</t>
-        </is>
-      </c>
-      <c r="D390" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
+    <row r="390" ht="20" customHeight="1">
+      <c r="A390" s="6" t="inlineStr">
+        <is>
+          <t>Categoria de lucrari: SPATII VERZI e Devize Formular F3 Lista cu cantitati de lucrari pe categorii de lucrari SECTIUNEA TEHNICA SECTIUNEA FINANCIARA Nr. Capitol de lucrari U.M. Cantitatea Pretul unitar (fara TVA) - Lei - TOTALUL (fara TVA) - Lei - 0 1 2 3 4 5 = 3 x 4 1 TSH01A1 - DEGAJAREA TERENULUI DE CORPURI STRAINE 100 MP. 59.180 186.53 11,039.13 material: 0.00 0.00 manopera: 186.53 11,039.13 utilaj: 0.00 0.00 transport: 0.00 0.00 2 TSC02C11 - SAPATURA CU EXCAVAT. PE PNEURI 0,21-0,39 MC PAMINT UMID.NATUR DESC. AUT. TER.CAT.1 IN COND.GOSP. APE 100 MC. 17.750 1,413.00 25,080.75 material: 0.00 0.00 manopera: 0.00 0.00 utilaj: 1,413.00 25,080.75 transport: 0.00 0.00 3 TRA01A10P - TRANSPORTUL RUTIER AL PAMINTULUI SAU MOLOZULUI CU AUTOBASCULANTA DIST. = 10 KM TONA 3,373.370 11.00 37,107.96 material: 0.00 0.00 manopera: 0.00 0.89 utilaj: 0.00 0.00 transport: 11.00 37,107.07 4 TSE04A1 - NIVELAREA SUPR. TEREN. SI PLATF.DE TERASM. EXEC.CU BULDOZ. PE TRACT. 65-80 CP IN TEREN CATEG. 1 SI 2 100 MP. 59.180 37.50 2,219.25 material: 0.00 0.00 manopera: 0.00 0.00 utilaj: 37.50 2,219.25 transport: 0.00 0.00 5 TSE01A1 - NIVELAREA MANUALA A TERENURILOR SI A PLATFORMELOR CU DENIVELARI DE 10-20 CM IN TEREN USOR 100 MP. 59.180 155.67 9,212.29 material: 0.00 0.00 manopera: 155.67 9,212.29 utilaj: 0.00 0.00 transport: 0.00 0.00 6 TSH05D1 - ASTERNEREA PAM. VEGETAL PE TEREN CU PANTA &lt; 20 %, IN STRAT. UNIFORME CU GROSIMEA DE 30CM MP. 5,918.000 4.75 28,105.29 material: 0.00 0.00 manopera: 4.75 28,105.29 utilaj: 0.00 0.00 transport: 0.00 0.00 6 2100001 - PAMANT VEGETAL M.C. 1,775.000 55.00 97,625.00 Deviz "005" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro) 80 Pagina 1 din 3</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" s="7" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B391" s="8" t="inlineStr">
         <is>
@@ -8241,8 +8207,8 @@
       </c>
       <c r="C391" s="8" t="inlineStr">
         <is>
-          <t>CD05C1  mc  60.0
-ZIDARIE DIN CARAMIDA TIP GVP LA CONSTR.H &lt; 35M, FORMAT 290X240X138MM, CAL. A material: manopera: utilaj: transport:</t>
+          <t>TSH01A1  mp  59.18
+DEGAJAREA TERENULUI DE CORPURI STRAINE material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D391" s="9" t="inlineStr">
@@ -8251,492 +8217,43 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="40" customHeight="1">
-      <c r="A392" s="7" t="n">
-        <v>354</v>
-      </c>
-      <c r="B392" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C392" s="8" t="inlineStr">
-        <is>
-          <t>$2100833  g  1065.0
-ADEZIV FAIANTA</t>
-        </is>
-      </c>
-      <c r="D392" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="393" ht="40" customHeight="1">
-      <c r="A393" s="7" t="n">
-        <v>355</v>
-      </c>
-      <c r="B393" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C393" s="8" t="inlineStr">
-        <is>
-          <t>$3270111  kg  106.5
-CHIT ROSTURI Deviz "002" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D393" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="394" ht="40" customHeight="1">
-      <c r="A394" s="7" t="n">
-        <v>356</v>
-      </c>
-      <c r="B394" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C394" s="8" t="inlineStr">
-        <is>
-          <t>CF15C#  mp  408.0
-Tencuieli interioare finisaj fin sclivisite, de 0.5 cm grosime, la pereti din beton cu suprafete plane, executate manual, cu mortar material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D394" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="395" ht="40" customHeight="1">
-      <c r="A395" s="7" t="n">
-        <v>357</v>
-      </c>
-      <c r="B395" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C395" s="8" t="inlineStr">
-        <is>
-          <t>CI06C#  mp  213.0
-Placaj faianta, aceeasi culoare si format, 15 cm - 30x30 cm, fixate cu aditiv, pe supr plane pereti si stalpi material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D395" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="396" ht="20" customHeight="1">
-      <c r="A396" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: INSTALATII ELECTRICE curenti tari OB.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="397" ht="40" customHeight="1">
-      <c r="A397" s="7" t="n">
-        <v>358</v>
-      </c>
-      <c r="B397" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C397" s="8" t="inlineStr">
-        <is>
-          <t>EA02A1  m  1450.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D397" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="398" ht="40" customHeight="1">
-      <c r="A398" s="7" t="n">
-        <v>359</v>
-      </c>
-      <c r="B398" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C398" s="8" t="inlineStr">
-        <is>
-          <t>EA02A1  m  95.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D398" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="399" ht="40" customHeight="1">
-      <c r="A399" s="7" t="n">
-        <v>360</v>
-      </c>
-      <c r="B399" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C399" s="8" t="inlineStr">
-        <is>
-          <t>EC05B1  m  1450.0
-CABLU ENERGIE TRAS PRIN TUB PROT METAL PT RACORD MOTOARE TABLOURI APARATE CONDUCTE 25 SAU 35 MMP material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D399" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="400" ht="40" customHeight="1">
-      <c r="A400" s="7" t="n">
-        <v>361</v>
-      </c>
-      <c r="B400" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C400" s="8" t="inlineStr">
-        <is>
-          <t>$2700014  ml  225.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "007" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D400" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="401" ht="40" customHeight="1">
-      <c r="A401" s="7" t="n">
-        <v>362</v>
-      </c>
-      <c r="B401" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C401" s="8" t="inlineStr">
-        <is>
-          <t>$3270430  m  95.0
-CABLU CYYF 3X1 5</t>
-        </is>
-      </c>
-      <c r="D401" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="402" ht="40" customHeight="1">
-      <c r="A402" s="7" t="n">
-        <v>363</v>
-      </c>
-      <c r="B402" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C402" s="8" t="inlineStr">
-        <is>
-          <t>EA02A1  m  225.0
-TUB IZOLANT DE PROTECTIE, ETANS IPE - PVC MONTAT INGROPAT CU D = 16MM material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D402" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="403" ht="40" customHeight="1">
-      <c r="A403" s="7" t="n">
-        <v>364</v>
-      </c>
-      <c r="B403" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C403" s="8" t="inlineStr">
-        <is>
-          <t>$2700014  ml  1486.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "008" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D403" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="404" ht="40" customHeight="1">
-      <c r="A404" s="7" t="n">
-        <v>365</v>
-      </c>
-      <c r="B404" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C404" s="8" t="inlineStr">
-        <is>
-          <t>$2700014  ml  95.0
-TUB DE PROTECTIE TIP IPEY / MONOFLEX D = 16 MM Deviz "006" - Formular F3 Formular generat cu programul eDevize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D404" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="405" ht="20" customHeight="1">
-      <c r="A405" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: ARHITECTURA VESTIARE FOTBALIST SI SALA FITNESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="406" ht="40" customHeight="1">
-      <c r="A406" s="7" t="n">
-        <v>366</v>
-      </c>
-      <c r="B406" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C406" s="8" t="inlineStr">
-        <is>
-          <t>$3276725  kg  4365.0
-TINCI PT TENCUIELI FINE</t>
-        </is>
-      </c>
-      <c r="D406" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="407" ht="40" customHeight="1">
-      <c r="A407" s="7" t="n">
-        <v>367</v>
-      </c>
-      <c r="B407" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C407" s="8" t="inlineStr">
-        <is>
-          <t>$2401678  mp  296.1
-FAIANTA</t>
-        </is>
-      </c>
-      <c r="D407" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="408" ht="40" customHeight="1">
-      <c r="A408" s="7" t="n">
-        <v>368</v>
-      </c>
-      <c r="B408" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C408" s="8" t="inlineStr">
-        <is>
-          <t>$3270111  kg  141.0
-CHIT ROSTURI Deviz "002" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D408" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="409" ht="40" customHeight="1">
-      <c r="A409" s="7" t="n">
-        <v>369</v>
-      </c>
-      <c r="B409" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C409" s="8" t="inlineStr">
-        <is>
-          <t>$2100833  g  1410.0
-ADEZIV FAIANTA</t>
-        </is>
-      </c>
-      <c r="D409" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="410" ht="40" customHeight="1">
-      <c r="A410" s="7" t="n">
-        <v>370</v>
-      </c>
-      <c r="B410" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C410" s="8" t="inlineStr">
-        <is>
-          <t>CI06C#  mp  282.0
-Placaj faianta, aceeasi culoare si format, 15 cm - 30x30 cm, fixate cu aditiv, pe supr plane pereti si stalpi material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D410" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="411" ht="40" customHeight="1">
-      <c r="A411" s="7" t="n">
-        <v>371</v>
-      </c>
-      <c r="B411" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C411" s="8" t="inlineStr">
-        <is>
-          <t>CF15C#  mp  873.0
-Tencuieli interioare finisaj fin sclivisite, de 0.5 cm grosime, la pereti din beton cu suprafete plane, executate manual, cu mortar material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D411" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="412" ht="20" customHeight="1">
-      <c r="A412" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA (vestiar e, sala fitness)</t>
-        </is>
-      </c>
-    </row>
-    <row r="413" ht="40" customHeight="1">
-      <c r="A413" s="7" t="n">
-        <v>372</v>
-      </c>
-      <c r="B413" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C413" s="8" t="inlineStr">
-        <is>
-          <t>$2100910  mc  15.12
-BETON MARFA CLASA C8 / 10 Deviz "001" - Formular F3 Formular generat cu programuf @Devize (www.eDevize.ro)</t>
-        </is>
-      </c>
-      <c r="D413" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
-    <row r="414" ht="20" customHeight="1">
-      <c r="A414" s="6" t="inlineStr">
-        <is>
-          <t>Categoria de lucrari: STRUCTURA DE REZISTENTA (vestiar, grupuri sanitare)</t>
-        </is>
-      </c>
-    </row>
-    <row r="415" ht="40" customHeight="1">
-      <c r="A415" s="7" t="n">
-        <v>373</v>
-      </c>
-      <c r="B415" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C415" s="8" t="inlineStr">
-        <is>
-          <t>TSC18B1  mc  0.7
-SAPAT.CU BULDOZ. PE TRACT. 65-80CP INCL. IMPINS PAMINTULUI LA 10 M TEREN CAT 2 material: manopera: utilaj: transport:</t>
-        </is>
-      </c>
-      <c r="D415" s="9" t="inlineStr">
-        <is>
-          <t>ARTICOL SUPLIMENTAR ÎN OFERTĂ</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A414:D414"/>
-    <mergeCell ref="A303:D303"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A348:D348"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A289:D289"/>
-    <mergeCell ref="A31:D31"/>
+  <mergeCells count="35">
+    <mergeCell ref="A321:D321"/>
+    <mergeCell ref="A311:D311"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A386:D386"/>
+    <mergeCell ref="A377:D377"/>
+    <mergeCell ref="A373:D373"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A288:D288"/>
     <mergeCell ref="A295:D295"/>
-    <mergeCell ref="A338:D338"/>
-    <mergeCell ref="A412:D412"/>
+    <mergeCell ref="A270:D270"/>
     <mergeCell ref="A368:D368"/>
-    <mergeCell ref="A405:D405"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A396:D396"/>
-    <mergeCell ref="A325:D325"/>
-    <mergeCell ref="A315:D315"/>
-    <mergeCell ref="A355:D355"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A271:D271"/>
+    <mergeCell ref="A340:D340"/>
+    <mergeCell ref="A300:D300"/>
+    <mergeCell ref="A358:D358"/>
+    <mergeCell ref="A334:D334"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A281:D281"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A364:D364"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A330:D330"/>
-    <mergeCell ref="A317:D317"/>
-    <mergeCell ref="A286:D286"/>
-    <mergeCell ref="A379:D379"/>
-    <mergeCell ref="A282:D282"/>
-    <mergeCell ref="A388:D388"/>
-    <mergeCell ref="A273:D273"/>
-    <mergeCell ref="A376:D376"/>
-    <mergeCell ref="A306:D306"/>
+    <mergeCell ref="A354:D354"/>
+    <mergeCell ref="A363:D363"/>
+    <mergeCell ref="A345:D345"/>
+    <mergeCell ref="A292:D292"/>
+    <mergeCell ref="A326:D326"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A285:D285"/>
+    <mergeCell ref="A365:D365"/>
+    <mergeCell ref="A272:D272"/>
+    <mergeCell ref="A390:D390"/>
+    <mergeCell ref="A302:D302"/>
     <mergeCell ref="A384:D384"/>
-    <mergeCell ref="A298:D298"/>
-    <mergeCell ref="A374:D374"/>
+    <mergeCell ref="A313:D313"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output_AO/Raport_Oferta_3.xlsx
+++ b/output_AO/Raport_Oferta_3.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>EE09B#  buc  23.0
+          <t>EE09B  buc  23.0
 CORP DE ILUMINAT SPECIAL DIFUZANT, PENTRU LAMPI CU VAPORI DE MERCUR, COMPLECT, CU BALAST, MONTAT PE BOLTURI IMPLANTATE</t>
         </is>
       </c>
@@ -874,7 +874,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>ED03B#  buc  44.0
+          <t>ED03B  buc  44.0
 APARAT DE COMUTARE (INTRERUPATOR, COMUTATOR, PRIZA) DE LA 32A LA 63A CU DIBLURI CU EXPANDARE</t>
         </is>
       </c>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>CC03C#  kg  3630.0
+          <t>CC03C  kg  3630.0
 Montare plasa sudate la inaltimi mai mici sau egal cu 35m, la placi</t>
         </is>
       </c>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>RPCE29A#  mp  1256.0
+          <t>RPCE29A  mp  1256.0
 PRELATA PENTRU PROTEJAREA TERASEI PE TIMP PLOIOS PE DURATA REFACERII</t>
         </is>
       </c>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>CK25A#  mp  7.0
+          <t>CK25A  mp  7.0
 USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
         </is>
       </c>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>CC03C#  kg  735.0
+          <t>CC03C  kg  735.0
 Montare plasa sudate la inaltimi mai mici sau egal cu 35m, la placi</t>
         </is>
       </c>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>RPCR21A#  mp  195.0
+          <t>RPCR21A  mp  195.0
 Vopsitorii interioare cu vopsea lavabila la pereti si tavane cu vopsea lavabila, pe glet de ipsos</t>
         </is>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>CG17B#  mp  79.0
+          <t>CG17B  mp  79.0
 Pardos placi gresie ceram patr, dreptungh, hexag, S 60 cmp/buc, incl str</t>
         </is>
       </c>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>CK25A#  mp  34.0
+          <t>CK25A  mp  34.0
 USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
         </is>
       </c>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>CK23A#  mp  6.0
+          <t>CK23A  mp  6.0
 Ferestre din mase plastice cu unul sau mai multe canaturi, supraf toc mai mare 1.00 mp, la ctii cu H mai mic sau egal 35 m</t>
         </is>
       </c>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>CK26A#  ml  9.0
+          <t>CK26A  ml  9.0
 Glafuri mase plastice, montate la ferestre</t>
         </is>
       </c>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>CE20A#  ml  19.0
+          <t>CE20A  ml  19.0
 Sistem de jgheaburi tip brass din tabla protejata anticorosiv</t>
         </is>
       </c>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>CE22A#  ml  7.0
+          <t>CE22A  ml  7.0
 Sisteme de burlane tip brass din tabla (protejata anticorosiv)</t>
         </is>
       </c>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>SA14D#  m  30.0
+          <t>SA14D  m  30.0
 TEAVA MAT PL (PP, PE, PP-R) IMBINATA PRIN SUDURA PRIN POLIFUZIUNE, LA CTII IND, D=32 MM</t>
         </is>
       </c>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>SB08B#  m  20.0
+          <t>SB08B  m  20.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP CUB PARD, DN =40MM</t>
         </is>
       </c>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>SA14E#  m  5.0
+          <t>SA14E  m  5.0
 TEAVA MAT PL (PP. PE, PP-R) IMBINATA PRIN SUDURA PRIN POLIFUZIUNE, LA CTII IND, D= 40MM</t>
         </is>
       </c>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>SD07B#  buc  8.0
+          <t>SD07B  buc  8.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D=3 /4''</t>
         </is>
       </c>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>SD07C#  buc  3.0
+          <t>SD07C  buc  3.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D= 1' '</t>
         </is>
       </c>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>SD07D#  buc  4.0
+          <t>SD07D  buc  4.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D= 11/4''</t>
         </is>
       </c>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>SF01C#  m  200.0
+          <t>SF01C  m  200.0
 EFECT PROBA ETANS PRES INSTAL APA CALDA, RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D= 16-110 MM</t>
         </is>
       </c>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>SF05C#  m  200.0
+          <t>SF05C  m  200.0
 SPALARE INSTAL APA RECE SAU CALDA EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>SB08A#  m  10.0
+          <t>SB08A  m  10.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC MONT APAR SAU INGROP SUB PARD, DN =32 MM</t>
         </is>
       </c>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>SB09A#  buc  10.0
+          <t>SB09A  buc  10.0
 PIESE LEG(COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN32 MM</t>
         </is>
       </c>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>SB08C#  m  5.0
+          <t>SB08C  m  5.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =50 MM</t>
         </is>
       </c>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>SB08D#  m  10.0
+          <t>SB08D  m  10.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =75 MM</t>
         </is>
       </c>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>SB08E#  m  35.0
+          <t>SB08E  m  35.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =110 MM</t>
         </is>
       </c>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>SB09E#  buc  3.0
+          <t>SB09E  buc  3.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=110MM</t>
         </is>
       </c>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>SB28A#  buc  4.0
+          <t>SB28A  buc  4.0
 SIFON DE PARDOSEALA DIN POLIPROPILENA, AVAND DIAMETRUL IESIRII DE 50 MM</t>
         </is>
       </c>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>SB27A#  buc  3.0
+          <t>SB27A  buc  3.0
 CACIULA VENTIL, TABLA, MONT PE COLOANE AERIS DIN TUBURI FONTA SAU GRESIE CERAM ANTIAC, D=50-150 MM</t>
         </is>
       </c>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>SF02C#  m  70.0
+          <t>SF02C  m  70.0
 EFECTUARE PROBA FUNCT INSTAL APA RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D=16-110 MM</t>
         </is>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>SF04A#  m  105.0
+          <t>SF04A  m  105.0
 EF PRB ETANS , FUNCT, INST CANAL DIN TUB FONTA SC, TEVI PVC (U) , PE, PP, PP-R FONTA DUCT.D=100MM BUC. MONTAT LAVOAR GRUP SANITAR - DESCRIERE:</t>
         </is>
       </c>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>SC04A#  buc  1.0
+          <t>SC04A  buc  1.0
 LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
         </is>
       </c>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t>SD04A#  buc  1.0
+          <t>SD04A  buc  1.0
 BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
         </is>
       </c>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>SC12A#  buc  1.0
+          <t>SC12A  buc  1.0
 ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
         </is>
       </c>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>SC13A#  buc  1.0
+          <t>SC13A  buc  1.0
 OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
         </is>
       </c>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>SC11A#  buc  1.0
+          <t>SC11A  buc  1.0
 PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
         </is>
       </c>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>SC14A#  buc  1.0
+          <t>SC14A  buc  1.0
 PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
         </is>
       </c>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>SC07A#  buc  1.0
+          <t>SC07A  buc  1.0
 VAS CLOS, ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
         </is>
       </c>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>SD05A#  buc  1.0
+          <t>SD05A  buc  1.0
 ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
         </is>
       </c>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>CC03C#  kg  3040.0
+          <t>CC03C  kg  3040.0
 Montare plasa sudate la inaltimi mai mici sau egal cu 35m, la placi</t>
         </is>
       </c>
@@ -8250,8 +8250,8 @@
       </c>
       <c r="C380" s="8" t="inlineStr">
         <is>
-          <t>IZD03D1  tona  8.0
-VOPSIRE CU VOPS MINIU CU APARAT AER COMPR 1 STR PECONF SI CTII METAL EXEC DIN PROF GROS 8-12 MM material: manopera: utilaj: transport:</t>
+          <t>IZD04D1  tona  8.0
+VOPSIRE CU APARAT AER COMPR VOPSEA ULEI PE CONF SICONSTR MET PROFILE 8-12MM 2STRATURI material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
         </is>
       </c>
       <c r="D380" s="9" t="inlineStr">
@@ -8271,8 +8271,8 @@
       </c>
       <c r="C381" s="8" t="inlineStr">
         <is>
-          <t>IZD04D1  tona  8.0
-VOPSIRE CU APARAT AER COMPR VOPSEA ULEI PE CONF SICONSTR MET PROFILE 8-12MM 2STRATURI material: manopera: utilaj: transport: Deviz "003" - Formular F3 Formular generat cu programul @Devize (www.eDevize.ro)</t>
+          <t>IZD03D1  tona  8.0
+VOPSIRE CU VOPS MINIU CU APARAT AER COMPR 1 STR PECONF SI CTII METAL EXEC DIN PROF GROS 8-12 MM material: manopera: utilaj: transport:</t>
         </is>
       </c>
       <c r="D381" s="9" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>CG08A#  mp  8404.0
+          <t>CG08A  mp  8404.0
 Pardoseli cu covor PVC lipit cu prenadez pe suport existent, curatate, inclusiv pervazurile PVC, Smai mare 16 mp</t>
         </is>
       </c>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>CC03C#  kg  735.0
+          <t>CC03C  kg  735.0
 Montare plasa sudate la inaltimi mai mici sau egal cu 35m, la placi</t>
         </is>
       </c>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="B471" s="8" t="inlineStr">
         <is>
-          <t>RPCR21A#  mp  591.0
+          <t>RPCR21A  mp  591.0
 Vopsitorii interioare cu vopsea lavabila la pereti si tavane cu vopsea lavabila, pe glet de ipsos</t>
         </is>
       </c>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B488" s="8" t="inlineStr">
         <is>
-          <t>CG17B#  mp  166.0
+          <t>CG17B  mp  166.0
 Pardos placi gresie ceram patr, dreptungh, hexag, S 60 cmp/buc, incl str</t>
         </is>
       </c>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B500" s="8" t="inlineStr">
         <is>
-          <t>CG01E#  mp  75.0
+          <t>CG01E  mp  75.0
 Strat suport pardoseli din ipsos de 3 cm grosime ( sapa autonivelanta )</t>
         </is>
       </c>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="B507" s="8" t="inlineStr">
         <is>
-          <t>RPCK14B#  ml  50.0
+          <t>RPCK14B  ml  50.0
 Plinte profil PVC , la pereti gata tencuiti, lipire cu Prenadez, imcl. reparare strat suport, S&gt;16 mp</t>
         </is>
       </c>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="B510" s="8" t="inlineStr">
         <is>
-          <t>CK25A#  mp  47.0
+          <t>CK25A  mp  47.0
 USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
         </is>
       </c>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="B514" s="8" t="inlineStr">
         <is>
-          <t>CK23A#  mp  26.0
+          <t>CK23A  mp  26.0
 Ferestre din mase plastice cu unul sau mai multe canaturi, supraf toc mai mare 1.00 mp, la ctii cu H mai mic sau egal 35 m</t>
         </is>
       </c>
@@ -11031,7 +11031,7 @@
       </c>
       <c r="B516" s="8" t="inlineStr">
         <is>
-          <t>CK26A#  ml  21.0
+          <t>CK26A  ml  21.0
 Glafuri mase plastice, montate la ferestre</t>
         </is>
       </c>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B531" s="8" t="inlineStr">
         <is>
-          <t>CE20A#  ml  14.0
+          <t>CE20A  ml  14.0
 Sistem de jgheaburi tip brass din tabla protejata anticorosiv</t>
         </is>
       </c>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="B533" s="8" t="inlineStr">
         <is>
-          <t>CE22A#  ml  14.0
+          <t>CE22A  ml  14.0
 Sisteme de burlane tip brass din tabla (protejata anticorosiv)</t>
         </is>
       </c>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="B543" s="8" t="inlineStr">
         <is>
-          <t>SA14D#  m  35.0
+          <t>SA14D  m  35.0
 TEAVA MAT PL (PP, PE, PP-R) IMBINATA PRIN SUDURA PRIN POLIFUZIUNE, LA CTII IND,D=32 MM</t>
         </is>
       </c>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B549" s="8" t="inlineStr">
         <is>
-          <t>SB08B#  m  20.0
+          <t>SB08B  m  20.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP CUB PARD, DN =40MM</t>
         </is>
       </c>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B551" s="8" t="inlineStr">
         <is>
-          <t>SA17D#  m  10.0
+          <t>SA17D  m  10.0
 TEAVA PP, PE, PP-R IMBIN SUD PRIN POLIFUZ, IN COND DISTRIB LA CLAD LOC SI SOC-CULT, D=50 MM</t>
         </is>
       </c>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="B557" s="8" t="inlineStr">
         <is>
-          <t>SD07B#  buc  9.0
+          <t>SD07B  buc  9.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D=3 /4''</t>
         </is>
       </c>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="B559" s="8" t="inlineStr">
         <is>
-          <t>SD07C#  buc  3.0
+          <t>SD07C  buc  3.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D= 1''</t>
         </is>
       </c>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="B561" s="8" t="inlineStr">
         <is>
-          <t>SD07D#  buc  3.0
+          <t>SD07D  buc  3.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE, PENTRU TEVI OTEL, D= 11/4''</t>
         </is>
       </c>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="B563" s="8" t="inlineStr">
         <is>
-          <t>SD07E#  buc  1.0
+          <t>SD07E  buc  1.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCATOARE, PENTRU TEVI OTEL, D=11/2''</t>
         </is>
       </c>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="B572" s="8" t="inlineStr">
         <is>
-          <t>SF01C#  m  180.0
+          <t>SF01C  m  180.0
 EFECT PROBA ETANS PRES INSTAL APA CALDA, RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D= 16-110 MM</t>
         </is>
       </c>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="B573" s="8" t="inlineStr">
         <is>
-          <t>SF05C#  m  180.0
+          <t>SF05C  m  180.0
 SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="B574" s="8" t="inlineStr">
         <is>
-          <t>SB08A#  m  10.0
+          <t>SB08A  m  10.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC MONT APAR SAU INGROP SUB PARD, DN =32 MM</t>
         </is>
       </c>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="B577" s="8" t="inlineStr">
         <is>
-          <t>SB08C#  m  5.0
+          <t>SB08C  m  5.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =50 MM</t>
         </is>
       </c>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="B579" s="8" t="inlineStr">
         <is>
-          <t>SB08D#  m  15.0
+          <t>SB08D  m  15.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =75 MM</t>
         </is>
       </c>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="B581" s="8" t="inlineStr">
         <is>
-          <t>SB08E#  m  45.0
+          <t>SB08E  m  45.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =110 MM</t>
         </is>
       </c>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B584" s="8" t="inlineStr">
         <is>
-          <t>SB09E#  buc  5.0
+          <t>SB09E  buc  5.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=110MM</t>
         </is>
       </c>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="B590" s="8" t="inlineStr">
         <is>
-          <t>SB27A#  buc  2.0
+          <t>SB27A  buc  2.0
 CACIULA VENTIL, TABLA, MONT PE COLOANE AERIS DIN TUBURI FONTA SAU GRESIE CERAM ANTIAC, D=50-150 MM</t>
         </is>
       </c>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B634" s="8" t="inlineStr">
         <is>
-          <t>SD02A#  buc  14.0
+          <t>SD02A  buc  14.0
 BATERIE BAIE AMESTEC, CU DUS FLEX SAU FIX, INDIF INCHID, INCL PT HAND, MOBT PE PERETI CARAM SAU BCA</t>
         </is>
       </c>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="B662" s="8" t="inlineStr">
         <is>
-          <t>IC31A1#  m  36.0
+          <t>IC31A1  m  36.0
 TEAVA DIN CUPRU MONTATA PRIN SUDURA LA LEGATURA CORPURILOR AI APARATELOR DE INSTALATIILE DE IMCALZIRE CENTRALA CU DIAMETRUL EXTERIOR DE PANA LA 15.0 MM INCLUSIV</t>
         </is>
       </c>
@@ -14237,7 +14237,7 @@
       </c>
       <c r="B672" s="8" t="inlineStr">
         <is>
-          <t>EE09B#  buc  54.0
+          <t>EE09B  buc  54.0
 CORP DE ILUMINAT SPECIAL DIFUZANT, PENTRU LAMPI CU VAPORI DE MERCUR, COMPLECT, CU BALAST, MONTAT PE BOLTURI IMPLANTATE</t>
         </is>
       </c>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="B681" s="8" t="inlineStr">
         <is>
-          <t>ED03B#  buc  102.0
+          <t>ED03B  buc  102.0
 APARAT DE COMUTARE (INTRERUPATOR, COMUTATOR, PRIZA) DE LA 32A LA 63A CU DIBLURI CU EXPANDARE</t>
         </is>
       </c>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B732" s="8" t="inlineStr">
         <is>
-          <t>CC03C#  kg  315.0
+          <t>CC03C  kg  315.0
 Montare plasa sudate la inaltimi mai mici sau egal cu 35m, la placi</t>
         </is>
       </c>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="B771" s="8" t="inlineStr">
         <is>
-          <t>RPCR21A#  mp  24.0
+          <t>RPCR21A  mp  24.0
 Vopsitorii interioare cu vopsea lavabila la pereti si tavane cu vopsea lavabila, pe glet de ipsos</t>
         </is>
       </c>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="B774" s="8" t="inlineStr">
         <is>
-          <t>CG17B#  mp  24.0
+          <t>CG17B  mp  24.0
 Pardos placi gresie ceram patr, dreptungh, hexag, S 60 cmp/buc, incl str</t>
         </is>
       </c>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="B786" s="8" t="inlineStr">
         <is>
-          <t>CK25A#  mp  15.0
+          <t>CK25A  mp  15.0
 USI PROFILURI MASE PLASTICE, 1 CANAT, SUPR. TOC MAI MIC SAU EGAL 7 MP, INC. ARMATURI SI ACCESORII, MONTATE IN ZID DE ORICE FEL LA C-TII CU H MAI MIC DE 35 M INCLUSIV</t>
         </is>
       </c>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="B788" s="8" t="inlineStr">
         <is>
-          <t>CK23A#  mp  5.0
+          <t>CK23A  mp  5.0
 Ferestre din mase plastice cu unul sau mai multe canaturi, supraf toc mai mare 1.00 mp, la ctii cu H mai mic sau egal 35 m</t>
         </is>
       </c>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="B790" s="8" t="inlineStr">
         <is>
-          <t>CK26A#  ml  9.0
+          <t>CK26A  ml  9.0
 Glafuri mase plastice, montate la ferestre</t>
         </is>
       </c>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="B805" s="8" t="inlineStr">
         <is>
-          <t>CE20A#  ml  7.0
+          <t>CE20A  ml  7.0
 Sistem de jgheaburi tip brass din tabla protejata anticorosiv</t>
         </is>
       </c>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="B807" s="8" t="inlineStr">
         <is>
-          <t>CE22A#  ml  6.0
+          <t>CE22A  ml  6.0
 Sisteme de burlane tip brass din tabla (protejata anticorosiv)</t>
         </is>
       </c>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="B818" s="8" t="inlineStr">
         <is>
-          <t>SA14D#  m  5.0
+          <t>SA14D  m  5.0
 TEAVA MAT PL (PP, PE, PP-R) IMBINATA PRIN SUDURA PRIN POLIFUZIUNE, LA CTII IND, D=32 MM</t>
         </is>
       </c>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="B825" s="8" t="inlineStr">
         <is>
-          <t>SD07B#  buc  4.0
+          <t>SD07B  buc  4.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE , PENTRU TEVI OTEL, D=3 /4''</t>
         </is>
       </c>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="B828" s="8" t="inlineStr">
         <is>
-          <t>SD07C#  buc  1.0
+          <t>SD07C  buc  1.0
 ROBINET DE TRECERE CU VENTIL SI MUFE, CU SAU FARA DESCARCARE , PENTRU TEVI OTEL, D= 1''</t>
         </is>
       </c>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="B835" s="8" t="inlineStr">
         <is>
-          <t>SF01C#  m  50.0
+          <t>SF01C  m  50.0
 EFECT PROBA ETANS PRES INSTAL APA CALDA, RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D= 16-110 MM</t>
         </is>
       </c>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B836" s="8" t="inlineStr">
         <is>
-          <t>SF05C#  m  50.0
+          <t>SF05C  m  50.0
 SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
@@ -17631,7 +17631,7 @@
       </c>
       <c r="B837" s="8" t="inlineStr">
         <is>
-          <t>SB08A#  m  5.0
+          <t>SB08A  m  5.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC MONT APAR SAU INGROP SUB PARD, DN =32 MM</t>
         </is>
       </c>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="B839" s="8" t="inlineStr">
         <is>
-          <t>SB08B#  m  5.0
+          <t>SB08B  m  5.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP CUB PARD, DN =40MM</t>
         </is>
       </c>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="B841" s="8" t="inlineStr">
         <is>
-          <t>SB09A#  buc  10.0
+          <t>SB09A  buc  10.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN32 MM</t>
         </is>
       </c>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="B843" s="8" t="inlineStr">
         <is>
-          <t>SB09B#  m  10.0
+          <t>SB09B  m  10.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=40 MM</t>
         </is>
       </c>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="B845" s="8" t="inlineStr">
         <is>
-          <t>SB08C#  m  5.0
+          <t>SB08C  m  5.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =50 MM</t>
         </is>
       </c>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="B847" s="8" t="inlineStr">
         <is>
-          <t>SB09C#  buc  2.0
+          <t>SB09C  buc  2.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=50MM</t>
         </is>
       </c>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B849" s="8" t="inlineStr">
         <is>
-          <t>SB08D#  m  6.0
+          <t>SB08D  m  6.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =75 MM</t>
         </is>
       </c>
@@ -17925,7 +17925,7 @@
       </c>
       <c r="B851" s="8" t="inlineStr">
         <is>
-          <t>SB08E#  m  20.0
+          <t>SB08E  m  20.0
 TEAVA PE, PP, PP-R PT CANAL, IMBIN CU GARN CAUCIUC, MONT APAR SAU INGROP SUB PARD, DN =110 MM</t>
         </is>
       </c>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="B854" s="8" t="inlineStr">
         <is>
-          <t>SB09E#  buc  4.0
+          <t>SB09E  buc  4.0
 PIESE LEG (COT, RED, PIESA CURAT MUFA DUBLA, COMP DILAT) PE, PP, PP-R CANAL IMB GRN CAUC DN=110MM</t>
         </is>
       </c>
@@ -18072,7 +18072,7 @@
       </c>
       <c r="B858" s="8" t="inlineStr">
         <is>
-          <t>SB28A#  buc  2.0
+          <t>SB28A  buc  2.0
 SIFON DE PARDOSEALA DIN POLIPROPILENA, AVAND DIAMETRUL IESIRII DE 50 MM</t>
         </is>
       </c>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B860" s="8" t="inlineStr">
         <is>
-          <t>SB27A#  buc  3.0
+          <t>SB27A  buc  3.0
 CACIULA VENTIL, TABLA, MONT PE COLOANE AERIS DIN TUBURI FONTA SAU GRESIE CERAM ANTIAC, D=50-150 MM</t>
         </is>
       </c>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="B884" s="8" t="inlineStr">
         <is>
-          <t>SC04A#  buc  1.0
+          <t>SC04A  buc  1.0
 LAVOAR SEMIPOT, PORTEL SAN, INCL PT HAND, TEVI SC PVC, PE CONS FIX PE PERETE ZID CARAM, BCA.</t>
         </is>
       </c>
@@ -18702,7 +18702,7 @@
       </c>
       <c r="B888" s="8" t="inlineStr">
         <is>
-          <t>SD04A#  buc  1.0
+          <t>SD04A  buc  1.0
 BATERIE AMESTEC BRAT BASCUL, STATIVA, PT LAVOAR SAU SPALATOR, INDIF INCHIDERE, INCL PT HAND, D=1/2''</t>
         </is>
       </c>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="B895" s="8" t="inlineStr">
         <is>
-          <t>SC12A#  buc  1.0
+          <t>SC12A  buc  1.0
 ETAJERA, PORTELAN SANITAR MONTATA PE PERETE DIN ZIDARIE CARAMIDA SAU BCA</t>
         </is>
       </c>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="B897" s="8" t="inlineStr">
         <is>
-          <t>SC13A#  buc  1.0
+          <t>SC13A  buc  1.0
 OGLINDA SANIT SEMICRIST, CU MARG SLEF, DE 400X500MM, 500X600 MM,ETC PE PER CARAM SI BCA</t>
         </is>
       </c>
@@ -18912,7 +18912,7 @@
       </c>
       <c r="B898" s="8" t="inlineStr">
         <is>
-          <t>SC11A#  buc  1.0
+          <t>SC11A  buc  1.0
 PORTPROSOP ALAMA NICHEL, BACHEL, ETC, MONT PE PER DIN ZID CARAM SAU BCA, UN PUNCT SPRIJIN</t>
         </is>
       </c>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="B899" s="8" t="inlineStr">
         <is>
-          <t>SC14A#  buc  1.0
+          <t>SC14A  buc  1.0
 PORTPAHAR, SAPUNIERA FONTA EM, PORTELAN SANIT, ETC, MONT PE PERETE DE CARAM SAU BCA</t>
         </is>
       </c>
@@ -19206,7 +19206,7 @@
       </c>
       <c r="B912" s="8" t="inlineStr">
         <is>
-          <t>SC07A#  buc  1.0
+          <t>SC07A  buc  1.0
 VAS CLOS , ECHIP, SEMIPORT, PORT SAN INCL PT HAND, ASEZ PE PARD, REZ APA LA INALT, SEMIINALT, SIF S</t>
         </is>
       </c>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="B915" s="8" t="inlineStr">
         <is>
-          <t>SD05A#  buc  1.0
+          <t>SD05A  buc  1.0
 ROBINET REGLAJ , DREPT SAU COLTAR, MONT INAINTEA ARMATURILOR DE LA OBIECTE SANIT, D=3/8''-1/2''</t>
         </is>
       </c>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="B939" s="8" t="inlineStr">
         <is>
-          <t>EE09B#  buc  11.0
+          <t>EE09B  buc  11.0
 CORP DE ILUMINAT SPECIAL DIFUZANT, PENTRU LAMPI CU VAPORI DE MERCUR, COMPLECT, CU BALAST, MONTAT PE BOLTURI IMPLANTATE</t>
         </is>
       </c>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="B946" s="8" t="inlineStr">
         <is>
-          <t>ED03B#  buc  9.0
+          <t>ED03B  buc  9.0
 APARAT DE COMUTARE (INTRERUPATOR, COMUTATOR, PRIZA) DE LA 32A LA 63A CU DIBLURI CU EXPANDARE</t>
         </is>
       </c>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="B987" s="8" t="inlineStr">
         <is>
-          <t>SE53A#  buc  1.0
+          <t>SE53A  buc  1.0
 CONTOR DE APA CU PALETE, CU RACORDURO OLANDEZE, AVAND DIAMETRUL DE 20-30 MM</t>
         </is>
       </c>
@@ -20801,7 +20801,7 @@
       </c>
       <c r="B992" s="8" t="inlineStr">
         <is>
-          <t>SE56A#  buc  1.0
+          <t>SE56A  buc  1.0
 FILTRU PENTRU APA POTABILA, CU MUFE FILETATE PENTRU MONTAJ PE CONDUCTA DIMENS 1''-2' '</t>
         </is>
       </c>
@@ -20990,7 +20990,7 @@
       </c>
       <c r="B1001" s="8" t="inlineStr">
         <is>
-          <t>SF01C#  m  345.0
+          <t>SF01C  m  345.0
 EFECT PROBA ETANS PRES INSTAL APA CALDA, RECE, DIN TEAVA PVC (G) SAU PE. PP. PP-R D= 16-110 MM</t>
         </is>
       </c>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B1002" s="8" t="inlineStr">
         <is>
-          <t>SF05C#  m  345.0
+          <t>SF05C  m  345.0
 SPALARE INSTAL APA RECE SAU CALDA , EXECUTATA DIN TEVI PVC (G) , PE, PP, PP-R, D= 20-75 MM</t>
         </is>
       </c>
@@ -21389,7 +21389,7 @@
       </c>
       <c r="B1020" s="8" t="inlineStr">
         <is>
-          <t>W2F03A#  buc  38.0
+          <t>W2F03A  buc  38.0
 Corp de iluminat exterior ornamental, pentru o lampa cu vapori de mercur sau sodiu montat pe stalp de metal de 5 m</t>
         </is>
       </c>
